--- a/docs/materie_prime.xlsx
+++ b/docs/materie_prime.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1096" uniqueCount="741">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1124" uniqueCount="766">
   <si>
     <t xml:space="preserve">Prodotto</t>
   </si>
@@ -944,16 +944,52 @@
     <t xml:space="preserve">  /* ---------- Stampa: A4, due colonne, niente colore di fondo ---------- */</t>
   </si>
   <si>
+    <t xml:space="preserve">.qr{</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  max-width:820px; margin:2.4rem auto .6rem; padding:0 1rem;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  display:flex; flex-direction:column; align-items:center; gap:.55rem; text-align:center;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">.qr svg{</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  width:104px; height:104px; display:block;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  background:#fff; padding:7px; border-radius:6px;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  border:2px solid var(--verde);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">.qr p{margin:0; font-size:.74rem; letter-spacing:.06em; text-transform:uppercase; font-weight:700; color:var(--verde)}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">.qr a{color:var(--verde); text-decoration:none; font-size:.78rem; letter-spacing:.01em; text-transform:none; font-weight:400}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">.qr a:hover{text-decoration:underline}</t>
+  </si>
+  <si>
     <t xml:space="preserve">.barra-stampa{</t>
   </si>
   <si>
-    <t xml:space="preserve">  display:flex; gap:.6rem; justify-content:center; flex-wrap:wrap;</t>
+    <t xml:space="preserve">  display:none;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  gap:.6rem; justify-content:center; flex-wrap:wrap;</t>
   </si>
   <si>
     <t xml:space="preserve">  margin:0 auto 2.2rem; padding:0 1rem; max-width:820px;</t>
   </si>
   <si>
-    <t xml:space="preserve">}</t>
+    <t xml:space="preserve">body.mostra-stampa .barra-stampa{display:flex}</t>
   </si>
   <si>
     <t xml:space="preserve">.barra-stampa button{</t>
@@ -998,6 +1034,24 @@
     <t xml:space="preserve">    .banchi,.chiusura{display:none}</t>
   </si>
   <si>
+    <t xml:space="preserve">    .qr{margin:6mm auto 0; padding:0; break-inside:avoid}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    .qr svg{width:74px; height:74px; border:1pt solid #000; padding:4px}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    .qr p{color:#000; font-size:7.5pt}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    .qr a{color:#000; font-size:7.5pt}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    body.stampa-colore .qr svg{border-color:var(--verde)}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    body.stampa-colore .qr p, body.stampa-colore .qr a{color:var(--verde)}</t>
+  </si>
+  <si>
     <t xml:space="preserve">    .wrap{max-width:none;padding:0}</t>
   </si>
   <si>
@@ -1229,6 +1283,12 @@
     <t xml:space="preserve">&lt;script&gt;</t>
   </si>
   <si>
+    <t xml:space="preserve">if(new URLSearchParams(location.search).has('print')){</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  document.body.classList.add('mostra-stampa');</t>
+  </si>
+  <si>
     <t xml:space="preserve">function stampa(colore){</t>
   </si>
   <si>
@@ -1248,6 +1308,21 @@
   </si>
   <si>
     <t xml:space="preserve">&lt;/script&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;div class="qr"&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;p&gt;Il menu sul telefono&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;svg viewBox="0 0 33 33" xmlns="http://www.w3.org/2000/svg" shape-rendering="crispEdges" role="img" aria-label="QR code del menu"&gt;&lt;rect width="33" height="33" fill="#fff"/&gt;&lt;path d="M2 2h7v1h-7zM13 2h5v1h-5zM21 2h2v1h-2zM24 2h7v1h-7zM2 3h1v1h-1zM8 3h1v1h-1zM13 3h6v1h-6zM22 3h1v1h-1zM24 3h1v1h-1zM30 3h1v1h-1zM2 4h1v1h-1zM4 4h3v1h-3zM8 4h1v1h-1zM10 4h3v1h-3zM15 4h1v1h-1zM17 4h1v1h-1zM20 4h1v1h-1zM24 4h1v1h-1zM26 4h3v1h-3zM30 4h1v1h-1zM2 5h1v1h-1zM4 5h3v1h-3zM8 5h1v1h-1zM10 5h2v1h-2zM13 5h2v1h-2zM16 5h2v1h-2zM19 5h1v1h-1zM21 5h1v1h-1zM24 5h1v1h-1zM26 5h3v1h-3zM30 5h1v1h-1zM2 6h1v1h-1zM4 6h3v1h-3zM8 6h1v1h-1zM10 6h4v1h-4zM17 6h6v1h-6zM24 6h1v1h-1zM26 6h3v1h-3zM30 6h1v1h-1zM2 7h1v1h-1zM8 7h1v1h-1zM10 7h2v1h-2zM20 7h1v1h-1zM22 7h1v1h-1zM24 7h1v1h-1zM30 7h1v1h-1zM2 8h7v1h-7zM10 8h1v1h-1zM12 8h1v1h-1zM14 8h1v1h-1zM16 8h1v1h-1zM18 8h1v1h-1zM20 8h1v1h-1zM22 8h1v1h-1zM24 8h7v1h-7zM10 9h5v1h-5zM16 9h1v1h-1zM18 9h1v1h-1zM20 9h3v1h-3zM2 10h1v1h-1zM4 10h5v1h-5zM12 10h2v1h-2zM18 10h2v1h-2zM24 10h5v1h-5zM2 11h3v1h-3zM9 11h2v1h-2zM13 11h5v1h-5zM21 11h6v1h-6zM30 11h1v1h-1zM2 12h2v1h-2zM5 12h1v1h-1zM8 12h2v1h-2zM12 12h1v1h-1zM14 12h5v1h-5zM23 12h1v1h-1zM26 12h1v1h-1zM3 13h4v1h-4zM9 13h1v1h-1zM12 13h1v1h-1zM14 13h2v1h-2zM17 13h1v1h-1zM21 13h2v1h-2zM25 13h3v1h-3zM29 13h1v1h-1zM2 14h2v1h-2zM6 14h1v1h-1zM8 14h3v1h-3zM12 14h1v1h-1zM14 14h1v1h-1zM16 14h2v1h-2zM19 14h1v1h-1zM21 14h1v1h-1zM25 14h1v1h-1zM27 14h2v1h-2zM4 15h1v1h-1zM7 15h1v1h-1zM11 15h1v1h-1zM13 15h2v1h-2zM17 15h2v1h-2zM20 15h2v1h-2zM23 15h4v1h-4zM30 15h1v1h-1zM4 16h1v1h-1zM8 16h2v1h-2zM12 16h2v1h-2zM19 16h2v1h-2zM27 16h2v1h-2zM7 17h1v1h-1zM9 17h2v1h-2zM13 17h1v1h-1zM16 17h1v1h-1zM18 17h1v1h-1zM20 17h3v1h-3zM24 17h2v1h-2zM29 17h1v1h-1zM2 18h2v1h-2zM7 18h2v1h-2zM12 18h1v1h-1zM14 18h1v1h-1zM18 18h3v1h-3zM22 18h1v1h-1zM27 18h2v1h-2zM2 19h1v1h-1zM5 19h1v1h-1zM7 19h1v1h-1zM10 19h1v1h-1zM12 19h2v1h-2zM15 19h3v1h-3zM19 19h3v1h-3zM23 19h4v1h-4zM28 19h1v1h-1zM30 19h1v1h-1zM2 20h1v1h-1zM5 20h1v1h-1zM8 20h1v1h-1zM10 20h2v1h-2zM13 20h1v1h-1zM15 20h5v1h-5zM24 20h3v1h-3zM28 20h1v1h-1zM2 21h1v1h-1zM5 21h1v1h-1zM9 21h1v1h-1zM11 21h2v1h-2zM14 21h2v1h-2zM17 21h1v1h-1zM20 21h2v1h-2zM24 21h1v1h-1zM26 21h1v1h-1zM29 21h1v1h-1zM2 22h1v1h-1zM4 22h7v1h-7zM12 22h3v1h-3zM16 22h2v1h-2zM19 22h1v1h-1zM22 22h5v1h-5zM28 22h3v1h-3zM10 23h2v1h-2zM17 23h6v1h-6zM26 23h5v1h-5zM2 24h7v1h-7zM11 24h1v1h-1zM13 24h1v1h-1zM20 24h3v1h-3zM24 24h1v1h-1zM26 24h3v1h-3zM2 25h1v1h-1zM8 25h1v1h-1zM10 25h3v1h-3zM14 25h1v1h-1zM16 25h1v1h-1zM18 25h1v1h-1zM22 25h1v1h-1zM26 25h1v1h-1zM29 25h2v1h-2zM2 26h1v1h-1zM4 26h3v1h-3zM8 26h1v1h-1zM10 26h1v1h-1zM12 26h1v1h-1zM19 26h1v1h-1zM22 26h5v1h-5zM28 26h1v1h-1zM30 26h1v1h-1zM2 27h1v1h-1zM4 27h3v1h-3zM8 27h1v1h-1zM10 27h2v1h-2zM14 27h4v1h-4zM19 27h2v1h-2zM23 27h1v1h-1zM27 27h2v1h-2zM2 28h1v1h-1zM4 28h3v1h-3zM8 28h1v1h-1zM10 28h1v1h-1zM12 28h1v1h-1zM14 28h2v1h-2zM17 28h3v1h-3zM24 28h6v1h-6zM2 29h1v1h-1zM8 29h1v1h-1zM11 29h2v1h-2zM14 29h1v1h-1zM18 29h1v1h-1zM21 29h3v1h-3zM25 29h1v1h-1zM27 29h1v1h-1zM29 29h1v1h-1zM2 30h7v1h-7zM10 30h1v1h-1zM12 30h2v1h-2zM16 30h1v1h-1zM19 30h2v1h-2zM23 30h2v1h-2zM26 30h3v1h-3z" fill="#000"/&gt;&lt;/svg&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;a href="https://santago2026.github.io/"&gt;santago2026.github.io&lt;/a&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;/div&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">&lt;footer class="chiusura"&gt;</t>
@@ -4539,27 +4614,27 @@
         <v>96</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>516</v>
+        <v>541</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>517</v>
+        <v>542</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>573</v>
+        <v>598</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>520</v>
+        <v>545</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>412</v>
+        <v>437</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>574</v>
+        <v>599</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>524</v>
+        <v>549</v>
       </c>
       <c r="C2" s="18" t="n">
         <v>20</v>
@@ -4573,15 +4648,15 @@
         <v>2.8731</v>
       </c>
       <c r="F2" s="57" t="s">
-        <v>575</v>
+        <v>600</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>576</v>
+        <v>601</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>577</v>
+        <v>602</v>
       </c>
       <c r="C3" s="18" t="n">
         <v>132</v>
@@ -4595,15 +4670,15 @@
         <v>0.0928863636363636</v>
       </c>
       <c r="F3" s="57" t="s">
-        <v>578</v>
+        <v>603</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>579</v>
+        <v>604</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>577</v>
+        <v>602</v>
       </c>
       <c r="C4" s="18" t="n">
         <v>132</v>
@@ -4617,15 +4692,15 @@
         <v>0.0938106060606061</v>
       </c>
       <c r="F4" s="57" t="s">
-        <v>578</v>
+        <v>603</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>580</v>
+        <v>605</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>581</v>
+        <v>606</v>
       </c>
       <c r="C5" s="18" t="n">
         <v>10</v>
@@ -4639,15 +4714,15 @@
         <v>1.144</v>
       </c>
       <c r="F5" s="57" t="s">
-        <v>582</v>
+        <v>607</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>583</v>
+        <v>608</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>584</v>
+        <v>609</v>
       </c>
       <c r="C6" s="18" t="n">
         <v>24</v>
@@ -4661,15 +4736,15 @@
         <v>0.6552</v>
       </c>
       <c r="F6" s="57" t="s">
-        <v>585</v>
+        <v>610</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>586</v>
+        <v>611</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>581</v>
+        <v>606</v>
       </c>
       <c r="C7" s="18" t="n">
         <v>10</v>
@@ -4683,15 +4758,15 @@
         <v>0.7238</v>
       </c>
       <c r="F7" s="57" t="s">
-        <v>587</v>
+        <v>612</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>588</v>
+        <v>613</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>581</v>
+        <v>606</v>
       </c>
       <c r="C8" s="18" t="n">
         <v>10</v>
@@ -4705,15 +4780,15 @@
         <v>1.419</v>
       </c>
       <c r="F8" s="57" t="s">
-        <v>582</v>
+        <v>607</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>589</v>
+        <v>614</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>581</v>
+        <v>606</v>
       </c>
       <c r="C9" s="18" t="n">
         <v>10</v>
@@ -4727,15 +4802,15 @@
         <v>1.4135</v>
       </c>
       <c r="F9" s="57" t="s">
-        <v>582</v>
+        <v>607</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>590</v>
+        <v>615</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>591</v>
+        <v>616</v>
       </c>
       <c r="C10" s="19" t="n">
         <f aca="false">Parametri!$B$45*Parametri!$B$46</f>
@@ -4750,15 +4825,15 @@
         <v>0.3146</v>
       </c>
       <c r="F10" s="57" t="s">
-        <v>592</v>
+        <v>617</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>593</v>
+        <v>618</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>594</v>
+        <v>619</v>
       </c>
       <c r="C11" s="18" t="n">
         <v>1680</v>
@@ -4772,15 +4847,15 @@
         <v>0.0338114285714286</v>
       </c>
       <c r="F11" s="57" t="s">
-        <v>595</v>
+        <v>620</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>596</v>
+        <v>621</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>597</v>
+        <v>622</v>
       </c>
       <c r="C12" s="18" t="n">
         <v>1000</v>
@@ -4794,15 +4869,15 @@
         <v>0.058804</v>
       </c>
       <c r="F12" s="57" t="s">
-        <v>598</v>
+        <v>623</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>599</v>
+        <v>624</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>600</v>
+        <v>625</v>
       </c>
       <c r="C13" s="18" t="n">
         <v>600</v>
@@ -4816,7 +4891,7 @@
         <v>0.020008</v>
       </c>
       <c r="F13" s="57" t="s">
-        <v>601</v>
+        <v>626</v>
       </c>
     </row>
   </sheetData>
@@ -4844,13 +4919,13 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="26" t="s">
-        <v>602</v>
+        <v>627</v>
       </c>
       <c r="B1" s="27"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="28" t="s">
-        <v>603</v>
+        <v>628</v>
       </c>
       <c r="B2" s="58" t="n">
         <v>100</v>
@@ -4858,7 +4933,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="28" t="s">
-        <v>604</v>
+        <v>629</v>
       </c>
       <c r="B3" s="59" t="n">
         <v>0.8</v>
@@ -4866,7 +4941,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="28" t="s">
-        <v>605</v>
+        <v>630</v>
       </c>
       <c r="B4" s="60" t="n">
         <f aca="false">B2</f>
@@ -4875,7 +4950,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="28" t="s">
-        <v>606</v>
+        <v>631</v>
       </c>
       <c r="B5" s="60" t="n">
         <f aca="false">B2*B3</f>
@@ -4884,7 +4959,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="28" t="s">
-        <v>607</v>
+        <v>632</v>
       </c>
       <c r="B6" s="60" t="n">
         <f aca="false">B2*(1-B3)</f>
@@ -4893,7 +4968,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="28" t="s">
-        <v>608</v>
+        <v>633</v>
       </c>
       <c r="B7" s="60" t="n">
         <f aca="false">B2</f>
@@ -4902,13 +4977,13 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="26" t="s">
-        <v>609</v>
+        <v>634</v>
       </c>
       <c r="B8" s="27"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="28" t="s">
-        <v>610</v>
+        <v>635</v>
       </c>
       <c r="B9" s="58" t="n">
         <v>200</v>
@@ -4916,7 +4991,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="28" t="s">
-        <v>611</v>
+        <v>636</v>
       </c>
       <c r="B10" s="59" t="n">
         <v>0.1</v>
@@ -4924,7 +4999,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="28" t="s">
-        <v>612</v>
+        <v>637</v>
       </c>
       <c r="B11" s="29" t="n">
         <v>0.92</v>
@@ -4932,7 +5007,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="28" t="s">
-        <v>613</v>
+        <v>638</v>
       </c>
       <c r="B12" s="61" t="n">
         <f aca="false">B9*B10/B11</f>
@@ -4941,7 +5016,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="28" t="s">
-        <v>614</v>
+        <v>639</v>
       </c>
       <c r="B13" s="58" t="n">
         <v>1</v>
@@ -4949,7 +5024,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="28" t="s">
-        <v>615</v>
+        <v>640</v>
       </c>
       <c r="B14" s="58" t="n">
         <v>1</v>
@@ -4957,7 +5032,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="28" t="s">
-        <v>616</v>
+        <v>641</v>
       </c>
       <c r="B15" s="58" t="n">
         <v>1</v>
@@ -4965,7 +5040,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="28" t="s">
-        <v>617</v>
+        <v>642</v>
       </c>
       <c r="B16" s="58" t="n">
         <v>1</v>
@@ -4973,7 +5048,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="28" t="s">
-        <v>618</v>
+        <v>643</v>
       </c>
       <c r="B17" s="58" t="n">
         <v>2</v>
@@ -4981,13 +5056,13 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="26" t="s">
-        <v>619</v>
+        <v>644</v>
       </c>
       <c r="B18" s="27"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="28" t="s">
-        <v>620</v>
+        <v>645</v>
       </c>
       <c r="B19" s="58" t="n">
         <v>300</v>
@@ -4995,7 +5070,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="28" t="s">
-        <v>621</v>
+        <v>646</v>
       </c>
       <c r="B20" s="58" t="n">
         <v>5</v>
@@ -5003,7 +5078,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="28" t="s">
-        <v>622</v>
+        <v>647</v>
       </c>
       <c r="B21" s="58" t="n">
         <v>25</v>
@@ -5011,7 +5086,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="28" t="s">
-        <v>623</v>
+        <v>648</v>
       </c>
       <c r="B22" s="58" t="n">
         <v>23</v>
@@ -5019,7 +5094,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="28" t="s">
-        <v>624</v>
+        <v>649</v>
       </c>
       <c r="B23" s="60" t="n">
         <f aca="false">B20*B21</f>
@@ -5028,7 +5103,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="28" t="s">
-        <v>625</v>
+        <v>650</v>
       </c>
       <c r="B24" s="60" t="n">
         <f aca="false">B19-B23</f>
@@ -5037,7 +5112,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="28" t="s">
-        <v>626</v>
+        <v>651</v>
       </c>
       <c r="B25" s="58" t="n">
         <v>4</v>
@@ -5045,7 +5120,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="28" t="s">
-        <v>627</v>
+        <v>652</v>
       </c>
       <c r="B26" s="58" t="n">
         <v>2</v>
@@ -5053,7 +5128,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="28" t="s">
-        <v>628</v>
+        <v>653</v>
       </c>
       <c r="B27" s="61" t="n">
         <f aca="false">B24*B25/(B25+B26)</f>
@@ -5062,7 +5137,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="28" t="s">
-        <v>629</v>
+        <v>654</v>
       </c>
       <c r="B28" s="61" t="n">
         <f aca="false">B24*B26/(B25+B26)</f>
@@ -5071,7 +5146,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="28" t="s">
-        <v>630</v>
+        <v>655</v>
       </c>
       <c r="B29" s="60" t="n">
         <f aca="false">B20*B22</f>
@@ -5080,13 +5155,13 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="26" t="s">
-        <v>631</v>
+        <v>656</v>
       </c>
       <c r="B30" s="27"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="28" t="s">
-        <v>632</v>
+        <v>657</v>
       </c>
       <c r="B31" s="58" t="n">
         <v>3</v>
@@ -5094,7 +5169,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="28" t="s">
-        <v>633</v>
+        <v>658</v>
       </c>
       <c r="B32" s="62" t="n">
         <v>24</v>
@@ -5102,7 +5177,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="28" t="s">
-        <v>634</v>
+        <v>659</v>
       </c>
       <c r="B33" s="63" t="n">
         <f aca="false">B31*B32*1.22</f>
@@ -5111,7 +5186,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="28" t="s">
-        <v>635</v>
+        <v>660</v>
       </c>
       <c r="B34" s="61" t="n">
         <f aca="false">'Vendite 2025'!$J$23</f>
@@ -5120,7 +5195,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="28" t="s">
-        <v>636</v>
+        <v>661</v>
       </c>
       <c r="B35" s="64" t="n">
         <f aca="false">B33/B34</f>
@@ -5129,13 +5204,13 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="26" t="s">
-        <v>637</v>
+        <v>662</v>
       </c>
       <c r="B36" s="27"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="28" t="s">
-        <v>638</v>
+        <v>663</v>
       </c>
       <c r="B37" s="58" t="n">
         <v>4</v>
@@ -5143,7 +5218,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="28" t="s">
-        <v>639</v>
+        <v>664</v>
       </c>
       <c r="B38" s="58" t="n">
         <v>7</v>
@@ -5151,7 +5226,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="28" t="s">
-        <v>640</v>
+        <v>665</v>
       </c>
       <c r="B39" s="65" t="n">
         <f aca="false">B40/B34</f>
@@ -5160,7 +5235,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="28" t="s">
-        <v>641</v>
+        <v>666</v>
       </c>
       <c r="B40" s="61" t="n">
         <f aca="false">'Fabbisogno 2026'!$D$51+'Fabbisogno 2026'!$D$52+'Fabbisogno 2026'!$D$53+'Fabbisogno 2026'!$D$54</f>
@@ -5169,7 +5244,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="28" t="s">
-        <v>642</v>
+        <v>667</v>
       </c>
       <c r="B41" s="61" t="n">
         <f aca="false">B31*B39</f>
@@ -5178,13 +5253,13 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="26" t="s">
-        <v>643</v>
+        <v>668</v>
       </c>
       <c r="B43" s="27"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="28" t="s">
-        <v>644</v>
+        <v>669</v>
       </c>
       <c r="B44" s="62" t="n">
         <v>1.5</v>
@@ -5192,7 +5267,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="28" t="s">
-        <v>645</v>
+        <v>670</v>
       </c>
       <c r="B45" s="58" t="n">
         <v>7</v>
@@ -5200,7 +5275,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="28" t="s">
-        <v>646</v>
+        <v>671</v>
       </c>
       <c r="B46" s="58" t="n">
         <v>4</v>
@@ -5208,7 +5283,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="28" t="s">
-        <v>647</v>
+        <v>672</v>
       </c>
       <c r="B47" s="62" t="n">
         <v>1</v>
@@ -5216,7 +5291,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="28" t="s">
-        <v>648</v>
+        <v>673</v>
       </c>
       <c r="B48" s="58" t="n">
         <v>20</v>
@@ -5224,7 +5299,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="28" t="s">
-        <v>649</v>
+        <v>674</v>
       </c>
       <c r="B49" s="58" t="n">
         <v>1</v>
@@ -5232,7 +5307,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="28" t="s">
-        <v>650</v>
+        <v>675</v>
       </c>
       <c r="B50" s="58" t="n">
         <v>1</v>
@@ -5240,7 +5315,7 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="28" t="s">
-        <v>651</v>
+        <v>676</v>
       </c>
       <c r="B51" s="58" t="n">
         <v>1</v>
@@ -5248,7 +5323,7 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="28" t="s">
-        <v>652</v>
+        <v>677</v>
       </c>
       <c r="B52" s="58" t="n">
         <v>1</v>
@@ -5256,7 +5331,7 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="28" t="s">
-        <v>653</v>
+        <v>678</v>
       </c>
       <c r="B53" s="58" t="n">
         <v>1</v>
@@ -5264,13 +5339,13 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="26" t="s">
-        <v>654</v>
+        <v>679</v>
       </c>
       <c r="B55" s="27"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="28" t="s">
-        <v>655</v>
+        <v>680</v>
       </c>
       <c r="B56" s="58" t="n">
         <v>120</v>
@@ -5278,7 +5353,7 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="28" t="s">
-        <v>611</v>
+        <v>636</v>
       </c>
       <c r="B57" s="59" t="n">
         <v>0.1</v>
@@ -5286,7 +5361,7 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="28" t="s">
-        <v>656</v>
+        <v>681</v>
       </c>
       <c r="B58" s="58" t="n">
         <v>1</v>
@@ -5294,7 +5369,7 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="28" t="s">
-        <v>657</v>
+        <v>682</v>
       </c>
       <c r="B59" s="58" t="n">
         <v>1</v>
@@ -5302,7 +5377,7 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="28" t="s">
-        <v>658</v>
+        <v>683</v>
       </c>
       <c r="B60" s="58" t="n">
         <v>1</v>
@@ -5310,7 +5385,7 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="28" t="s">
-        <v>659</v>
+        <v>684</v>
       </c>
       <c r="B61" s="58" t="n">
         <v>1</v>
@@ -5318,7 +5393,7 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="28" t="s">
-        <v>660</v>
+        <v>685</v>
       </c>
       <c r="B62" s="58" t="n">
         <v>2</v>
@@ -5326,13 +5401,13 @@
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="26" t="s">
-        <v>661</v>
+        <v>686</v>
       </c>
       <c r="B64" s="27"/>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="28" t="s">
-        <v>655</v>
+        <v>680</v>
       </c>
       <c r="B65" s="58" t="n">
         <v>150</v>
@@ -5340,7 +5415,7 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="28" t="s">
-        <v>611</v>
+        <v>636</v>
       </c>
       <c r="B66" s="59" t="n">
         <v>0.1</v>
@@ -5348,7 +5423,7 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="28" t="s">
-        <v>656</v>
+        <v>681</v>
       </c>
       <c r="B67" s="58" t="n">
         <v>1</v>
@@ -5356,7 +5431,7 @@
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="28" t="s">
-        <v>657</v>
+        <v>682</v>
       </c>
       <c r="B68" s="58" t="n">
         <v>1</v>
@@ -5364,7 +5439,7 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="28" t="s">
-        <v>658</v>
+        <v>683</v>
       </c>
       <c r="B69" s="58" t="n">
         <v>0</v>
@@ -5372,7 +5447,7 @@
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="28" t="s">
-        <v>659</v>
+        <v>684</v>
       </c>
       <c r="B70" s="58" t="n">
         <v>1</v>
@@ -5380,7 +5455,7 @@
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="28" t="s">
-        <v>660</v>
+        <v>685</v>
       </c>
       <c r="B71" s="58" t="n">
         <v>2</v>
@@ -5388,13 +5463,13 @@
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="26" t="s">
-        <v>662</v>
+        <v>687</v>
       </c>
       <c r="B73" s="27"/>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="28" t="s">
-        <v>663</v>
+        <v>688</v>
       </c>
       <c r="B74" s="58" t="n">
         <v>1</v>
@@ -5402,7 +5477,7 @@
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="28" t="s">
-        <v>664</v>
+        <v>689</v>
       </c>
       <c r="B75" s="58" t="n">
         <v>1</v>
@@ -5410,13 +5485,13 @@
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="26" t="s">
-        <v>665</v>
+        <v>690</v>
       </c>
       <c r="B77" s="27"/>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="28" t="s">
-        <v>666</v>
+        <v>691</v>
       </c>
       <c r="B78" s="58" t="n">
         <v>200</v>
@@ -5424,7 +5499,7 @@
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="28" t="s">
-        <v>611</v>
+        <v>636</v>
       </c>
       <c r="B79" s="59" t="n">
         <v>0.1</v>
@@ -5432,7 +5507,7 @@
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="28" t="s">
-        <v>656</v>
+        <v>681</v>
       </c>
       <c r="B80" s="58" t="n">
         <v>2</v>
@@ -5440,7 +5515,7 @@
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="28" t="s">
-        <v>657</v>
+        <v>682</v>
       </c>
       <c r="B81" s="58" t="n">
         <v>2</v>
@@ -5448,7 +5523,7 @@
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="28" t="s">
-        <v>658</v>
+        <v>683</v>
       </c>
       <c r="B82" s="58" t="n">
         <v>2</v>
@@ -5456,7 +5531,7 @@
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="28" t="s">
-        <v>659</v>
+        <v>684</v>
       </c>
       <c r="B83" s="58" t="n">
         <v>2</v>
@@ -5464,7 +5539,7 @@
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="28" t="s">
-        <v>660</v>
+        <v>685</v>
       </c>
       <c r="B84" s="58" t="n">
         <v>3</v>
@@ -5503,31 +5578,31 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>667</v>
+        <v>692</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>668</v>
+        <v>693</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>669</v>
+        <v>694</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>670</v>
+        <v>695</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>671</v>
+        <v>696</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>672</v>
+        <v>697</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>673</v>
+        <v>698</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>674</v>
+        <v>699</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>675</v>
+        <v>700</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6268,7 +6343,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="17" t="s">
-        <v>676</v>
+        <v>701</v>
       </c>
     </row>
   </sheetData>
@@ -6300,7 +6375,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="45" t="s">
-        <v>677</v>
+        <v>702</v>
       </c>
       <c r="B1" s="27"/>
       <c r="C1" s="27"/>
@@ -6311,13 +6386,13 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="26" t="s">
-        <v>678</v>
+        <v>703</v>
       </c>
       <c r="B3" s="27"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="28" t="s">
-        <v>679</v>
+        <v>704</v>
       </c>
       <c r="B4" s="62" t="n">
         <v>4</v>
@@ -6325,7 +6400,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="28" t="s">
-        <v>680</v>
+        <v>705</v>
       </c>
       <c r="B5" s="62" t="n">
         <v>120</v>
@@ -6333,7 +6408,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="28" t="s">
-        <v>681</v>
+        <v>706</v>
       </c>
       <c r="B6" s="58" t="n">
         <v>7</v>
@@ -6341,7 +6416,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="28" t="s">
-        <v>682</v>
+        <v>707</v>
       </c>
       <c r="B7" s="58" t="n">
         <v>400</v>
@@ -6349,7 +6424,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="28" t="s">
-        <v>683</v>
+        <v>708</v>
       </c>
       <c r="B8" s="62" t="n">
         <v>9.5</v>
@@ -6357,13 +6432,13 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="26" t="s">
-        <v>684</v>
+        <v>709</v>
       </c>
       <c r="B9" s="27"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="28" t="s">
-        <v>685</v>
+        <v>710</v>
       </c>
       <c r="B10" s="71" t="n">
         <f aca="false">B4</f>
@@ -6372,7 +6447,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="28" t="s">
-        <v>686</v>
+        <v>711</v>
       </c>
       <c r="B11" s="71" t="n">
         <f aca="false">'Prezzi Unitari'!$E$10</f>
@@ -6381,7 +6456,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="28" t="s">
-        <v>505</v>
+        <v>530</v>
       </c>
       <c r="B12" s="71" t="n">
         <f aca="false">Parametri!$B$48/100*'Prezzi Unitari'!$E$7</f>
@@ -6390,7 +6465,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="28" t="s">
-        <v>687</v>
+        <v>712</v>
       </c>
       <c r="B13" s="71" t="n">
         <f aca="false">Parametri!$B$78/1000*'Materie Prime IperTosano'!$H$4</f>
@@ -6399,7 +6474,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="28" t="s">
-        <v>688</v>
+        <v>713</v>
       </c>
       <c r="B14" s="71" t="n">
         <f aca="false">Parametri!$B$78*Parametri!$B$79/0.92/1000*'Prezzi Unitari'!$E$2</f>
@@ -6408,7 +6483,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="28" t="s">
-        <v>689</v>
+        <v>714</v>
       </c>
       <c r="B15" s="71" t="n">
         <f aca="false">Parametri!$B$82*'Prezzi Unitari'!$E$3+Parametri!$B$83*'Prezzi Unitari'!$E$4</f>
@@ -6417,7 +6492,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="28" t="s">
-        <v>690</v>
+        <v>715</v>
       </c>
       <c r="B16" s="71" t="n">
         <f aca="false">Parametri!$B$84*'Prezzi Unitari'!$E$13</f>
@@ -6426,7 +6501,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="72" t="s">
-        <v>691</v>
+        <v>716</v>
       </c>
       <c r="B17" s="71" t="n">
         <f aca="false">Parametri!$B$80*'Prezzi Unitari'!$E$12</f>
@@ -6435,7 +6510,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="28" t="s">
-        <v>692</v>
+        <v>717</v>
       </c>
       <c r="B18" s="71" t="n">
         <f aca="false">Parametri!$B$81*'Prezzi Unitari'!$E$11</f>
@@ -6444,7 +6519,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="68" t="s">
-        <v>693</v>
+        <v>718</v>
       </c>
       <c r="B19" s="23" t="n">
         <f aca="false">SUM(B10:B18)</f>
@@ -6453,13 +6528,13 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="26" t="s">
-        <v>694</v>
+        <v>719</v>
       </c>
       <c r="B21" s="27"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="28" t="s">
-        <v>695</v>
+        <v>720</v>
       </c>
       <c r="B22" s="73" t="n">
         <f aca="false">B8-B19</f>
@@ -6468,7 +6543,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="28" t="s">
-        <v>696</v>
+        <v>721</v>
       </c>
       <c r="B23" s="73" t="n">
         <f aca="false">B5*B6</f>
@@ -6477,7 +6552,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="28" t="s">
-        <v>697</v>
+        <v>722</v>
       </c>
       <c r="B24" s="73" t="n">
         <f aca="false">B7*B8</f>
@@ -6486,7 +6561,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="28" t="s">
-        <v>698</v>
+        <v>723</v>
       </c>
       <c r="B25" s="73" t="n">
         <f aca="false">B7*B19</f>
@@ -6495,7 +6570,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="35" t="s">
-        <v>699</v>
+        <v>724</v>
       </c>
       <c r="B26" s="74" t="n">
         <f aca="false">B24-B25-B23</f>
@@ -6504,7 +6579,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="28" t="s">
-        <v>700</v>
+        <v>725</v>
       </c>
       <c r="B27" s="75" t="n">
         <f aca="false">IF(B24=0,"",B26/B24)</f>
@@ -6513,7 +6588,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="35" t="s">
-        <v>701</v>
+        <v>726</v>
       </c>
       <c r="B28" s="76" t="n">
         <f aca="false">IF(B22&lt;=0,"mai",ROUNDUP(B23/B22,0))</f>
@@ -6522,7 +6597,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="77" t="s">
-        <v>702</v>
+        <v>727</v>
       </c>
       <c r="B29" s="78" t="n">
         <f aca="false">IF(B22&lt;=0,"mai",ROUNDUP(B5/B22,0))</f>
@@ -6535,27 +6610,27 @@
     </row>
     <row r="30" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="s">
-        <v>703</v>
+        <v>728</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>704</v>
+        <v>729</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>705</v>
+        <v>730</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>706</v>
+        <v>731</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>707</v>
+        <v>732</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>708</v>
+        <v>733</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="28" t="s">
-        <v>709</v>
+        <v>734</v>
       </c>
       <c r="B31" s="75" t="n">
         <v>0.0973655121591747</v>
@@ -6579,7 +6654,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="28" t="s">
-        <v>710</v>
+        <v>735</v>
       </c>
       <c r="B32" s="75" t="n">
         <v>0.106392778187178</v>
@@ -6603,7 +6678,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="28" t="s">
-        <v>711</v>
+        <v>736</v>
       </c>
       <c r="B33" s="75" t="n">
         <v>0.139646278555637</v>
@@ -6627,7 +6702,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="28" t="s">
-        <v>712</v>
+        <v>737</v>
       </c>
       <c r="B34" s="75" t="n">
         <v>0.205278187177598</v>
@@ -6651,7 +6726,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="28" t="s">
-        <v>713</v>
+        <v>738</v>
       </c>
       <c r="B35" s="75" t="n">
         <v>0.106392778187178</v>
@@ -6675,7 +6750,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="28" t="s">
-        <v>714</v>
+        <v>739</v>
       </c>
       <c r="B36" s="75" t="n">
         <v>0.139646278555637</v>
@@ -6699,7 +6774,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="28" t="s">
-        <v>715</v>
+        <v>740</v>
       </c>
       <c r="B37" s="75" t="n">
         <v>0.205278187177598</v>
@@ -6745,7 +6820,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="26" t="s">
-        <v>716</v>
+        <v>741</v>
       </c>
       <c r="B40" s="27"/>
       <c r="C40" s="27"/>
@@ -6755,7 +6830,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="77" t="s">
-        <v>717</v>
+        <v>742</v>
       </c>
       <c r="B41" s="30" t="n">
         <v>250</v>
@@ -6900,17 +6975,17 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="17" t="s">
-        <v>718</v>
+        <v>743</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="17" t="s">
-        <v>719</v>
+        <v>744</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="82" t="s">
-        <v>720</v>
+        <v>745</v>
       </c>
     </row>
   </sheetData>
@@ -6938,7 +7013,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="45" t="s">
-        <v>721</v>
+        <v>746</v>
       </c>
       <c r="B1" s="27"/>
       <c r="C1" s="27"/>
@@ -6949,25 +7024,25 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="26" t="s">
-        <v>722</v>
+        <v>747</v>
       </c>
       <c r="B3" s="27"/>
       <c r="C3" s="27"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="30" t="s">
-        <v>723</v>
+        <v>748</v>
       </c>
       <c r="B4" s="30" t="s">
-        <v>724</v>
+        <v>749</v>
       </c>
       <c r="C4" s="30" t="s">
-        <v>725</v>
+        <v>750</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="28" t="s">
-        <v>655</v>
+        <v>680</v>
       </c>
       <c r="B5" s="58" t="n">
         <v>120</v>
@@ -6978,7 +7053,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="28" t="s">
-        <v>611</v>
+        <v>636</v>
       </c>
       <c r="B6" s="59" t="n">
         <v>0.1</v>
@@ -6989,7 +7064,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="28" t="s">
-        <v>656</v>
+        <v>681</v>
       </c>
       <c r="B7" s="58" t="n">
         <v>1</v>
@@ -7000,7 +7075,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="28" t="s">
-        <v>657</v>
+        <v>682</v>
       </c>
       <c r="B8" s="58" t="n">
         <v>1</v>
@@ -7011,7 +7086,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="28" t="s">
-        <v>658</v>
+        <v>683</v>
       </c>
       <c r="B9" s="58" t="n">
         <v>1</v>
@@ -7022,7 +7097,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="28" t="s">
-        <v>659</v>
+        <v>684</v>
       </c>
       <c r="B10" s="58" t="n">
         <v>1</v>
@@ -7033,7 +7108,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="28" t="s">
-        <v>660</v>
+        <v>685</v>
       </c>
       <c r="B11" s="58" t="n">
         <v>2</v>
@@ -7044,25 +7119,25 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="26" t="s">
-        <v>726</v>
+        <v>751</v>
       </c>
       <c r="B13" s="27"/>
       <c r="C13" s="27"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="30" t="s">
-        <v>727</v>
+        <v>752</v>
       </c>
       <c r="B14" s="30" t="s">
-        <v>724</v>
+        <v>749</v>
       </c>
       <c r="C14" s="30" t="s">
-        <v>725</v>
+        <v>750</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="28" t="s">
-        <v>728</v>
+        <v>753</v>
       </c>
       <c r="B15" s="71" t="n">
         <f aca="false">B5/1000*'Materie Prime IperTosano'!$H$6</f>
@@ -7075,7 +7150,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="28" t="s">
-        <v>688</v>
+        <v>713</v>
       </c>
       <c r="B16" s="71" t="n">
         <f aca="false">B5*B6/0.92/1000*'Prezzi Unitari'!$E$2</f>
@@ -7088,7 +7163,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="28" t="s">
-        <v>689</v>
+        <v>714</v>
       </c>
       <c r="B17" s="71" t="n">
         <f aca="false">B9*'Prezzi Unitari'!$E$3+B10*'Prezzi Unitari'!$E$4</f>
@@ -7101,7 +7176,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="28" t="s">
-        <v>729</v>
+        <v>754</v>
       </c>
       <c r="B18" s="71" t="n">
         <f aca="false">B7*'Prezzi Unitari'!$E$12</f>
@@ -7114,7 +7189,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="28" t="s">
-        <v>730</v>
+        <v>755</v>
       </c>
       <c r="B19" s="71" t="n">
         <f aca="false">B8*'Prezzi Unitari'!$E$11</f>
@@ -7127,7 +7202,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="28" t="s">
-        <v>690</v>
+        <v>715</v>
       </c>
       <c r="B20" s="71" t="n">
         <f aca="false">B11*'Prezzi Unitari'!$E$13</f>
@@ -7140,7 +7215,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="20" t="s">
-        <v>731</v>
+        <v>756</v>
       </c>
       <c r="B21" s="23" t="n">
         <f aca="false">SUM(B15:B20)</f>
@@ -7153,7 +7228,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="26" t="s">
-        <v>732</v>
+        <v>757</v>
       </c>
       <c r="B23" s="27"/>
       <c r="C23" s="27"/>
@@ -7162,19 +7237,19 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="83" t="s">
-        <v>733</v>
+        <v>758</v>
       </c>
       <c r="B24" s="83" t="s">
-        <v>734</v>
+        <v>759</v>
       </c>
       <c r="C24" s="83" t="s">
-        <v>735</v>
+        <v>760</v>
       </c>
       <c r="D24" s="83" t="s">
-        <v>736</v>
+        <v>761</v>
       </c>
       <c r="E24" s="83" t="s">
-        <v>737</v>
+        <v>762</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7284,17 +7359,17 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="17" t="s">
-        <v>738</v>
+        <v>763</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="17" t="s">
-        <v>739</v>
+        <v>764</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="82" t="s">
-        <v>740</v>
+        <v>765</v>
       </c>
     </row>
   </sheetData>
@@ -9597,7 +9672,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:A477"/>
+  <dimension ref="A1:A510"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="120"/>
@@ -10635,324 +10710,320 @@
       <c r="A212" s="41"/>
     </row>
     <row r="213" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A213" s="41" t="s">
-        <v>303</v>
-      </c>
+      <c r="A213" s="41"/>
     </row>
     <row r="214" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A214" s="41" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="215" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A215" s="41" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="216" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A216" s="41" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="217" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A217" s="41" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="218" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A218" s="41" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="219" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A219" s="41" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="220" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A220" s="41" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="221" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A221" s="41" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="222" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A222" s="41" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
     </row>
     <row r="223" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A223" s="41" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
     </row>
     <row r="224" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A224" s="41" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="225" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A225" s="41" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="226" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A226" s="41" t="s">
-        <v>315</v>
-      </c>
+      <c r="A226" s="41"/>
     </row>
     <row r="227" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A227" s="41" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="228" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A228" s="41"/>
+      <c r="A228" s="41" t="s">
+        <v>315</v>
+      </c>
     </row>
     <row r="229" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A229" s="41" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="230" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A230" s="41" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="231" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A231" s="41" t="s">
-        <v>319</v>
+        <v>306</v>
       </c>
     </row>
     <row r="232" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A232" s="41" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="233" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A233" s="41" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="234" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A234" s="41" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="235" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A235" s="41" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="236" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A236" s="41" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="237" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A237" s="41" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="238" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A238" s="41" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="239" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A239" s="41" t="s">
-        <v>327</v>
+        <v>306</v>
       </c>
     </row>
     <row r="240" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A240" s="41" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
     </row>
     <row r="241" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A241" s="41" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
     </row>
     <row r="242" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A242" s="41" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
     </row>
     <row r="243" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A243" s="41" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
     </row>
     <row r="244" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A244" s="41" t="s">
-        <v>332</v>
-      </c>
+      <c r="A244" s="41"/>
     </row>
     <row r="245" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A245" s="41" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
     </row>
     <row r="246" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A246" s="41" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
     </row>
     <row r="247" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A247" s="41" t="s">
-        <v>324</v>
+        <v>331</v>
       </c>
     </row>
     <row r="248" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A248" s="41" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
     </row>
     <row r="249" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A249" s="41" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
     </row>
     <row r="250" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A250" s="41" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
     </row>
     <row r="251" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A251" s="41" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
     </row>
     <row r="252" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A252" s="41" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
     </row>
     <row r="253" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A253" s="41" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
     </row>
     <row r="254" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A254" s="41" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
     </row>
     <row r="255" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A255" s="41" t="s">
-        <v>342</v>
-      </c>
+      <c r="A255" s="41"/>
     </row>
     <row r="256" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A256" s="41" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
     </row>
     <row r="257" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A257" s="41" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
     </row>
     <row r="258" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A258" s="41" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
     </row>
     <row r="259" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A259" s="41"/>
+      <c r="A259" s="41" t="s">
+        <v>342</v>
+      </c>
     </row>
     <row r="260" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A260" s="41" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
     </row>
     <row r="261" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A261" s="41" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
     </row>
     <row r="262" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A262" s="41" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="263" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A263" s="41" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
     </row>
     <row r="264" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A264" s="41" t="s">
-        <v>324</v>
+        <v>347</v>
       </c>
     </row>
     <row r="265" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A265" s="41" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="266" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A266" s="41" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="267" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A267" s="41" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="268" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A268" s="41" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="269" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A269" s="41" t="s">
-        <v>324</v>
+        <v>352</v>
       </c>
     </row>
     <row r="270" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A270" s="41" t="s">
-        <v>354</v>
+        <v>342</v>
       </c>
     </row>
     <row r="271" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A271" s="41" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
     </row>
     <row r="272" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A272" s="41" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="273" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A273" s="41" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
     </row>
     <row r="274" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A274" s="41" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
     </row>
     <row r="275" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A275" s="41" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
     </row>
     <row r="276" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A276" s="41" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="277" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A277" s="41" t="s">
-        <v>324</v>
+        <v>359</v>
       </c>
     </row>
     <row r="278" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10976,47 +11047,47 @@
       </c>
     </row>
     <row r="282" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A282" s="41" t="s">
-        <v>364</v>
-      </c>
+      <c r="A282" s="41"/>
     </row>
     <row r="283" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A283" s="41" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="284" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A284" s="41" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="285" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A285" s="41" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="286" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A286" s="41" t="s">
-        <v>180</v>
+        <v>367</v>
       </c>
     </row>
     <row r="287" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A287" s="41" t="s">
-        <v>368</v>
+        <v>342</v>
       </c>
     </row>
     <row r="288" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A288" s="41" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="289" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A289" s="41" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="290" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A290" s="41" t="s">
         <v>370</v>
       </c>
-    </row>
-    <row r="290" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A290" s="41"/>
     </row>
     <row r="291" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A291" s="41" t="s">
@@ -11025,946 +11096,952 @@
     </row>
     <row r="292" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A292" s="41" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="293" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A293" s="41" t="s">
         <v>372</v>
       </c>
     </row>
-    <row r="293" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A293" s="42" t="str">
+    <row r="294" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A294" s="41" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="295" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A295" s="41" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="296" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A296" s="41" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="297" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A297" s="41" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="298" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A298" s="41" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="299" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A299" s="41" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="300" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A300" s="41" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="301" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A301" s="41" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="302" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A302" s="41" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="303" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A303" s="41" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="304" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A304" s="41" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="305" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A305" s="41" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="306" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A306" s="41" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="307" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A307" s="41" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="308" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A308" s="41" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="309" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A309" s="41" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="310" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A310" s="41" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="311" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A311" s="41" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="312" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A312" s="41" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="313" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A313" s="41"/>
+    </row>
+    <row r="314" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A314" s="41" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="315" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A315" s="41" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="316" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A316" s="42" t="str">
         <f aca="false">"    &lt;p class=""occhiello""&gt;"&amp;'Testi Menu'!$B$5&amp;"&lt;/p&gt;"</f>
         <v>    &lt;p class="occhiello"&gt;Parrocchia di Sant'Agostino · Ferrara&lt;/p&gt;</v>
       </c>
     </row>
-    <row r="294" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A294" s="42" t="str">
+    <row r="317" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A317" s="42" t="str">
         <f aca="false">"    &lt;h1 class=""titolo""&gt;&lt;span class=""riga1""&gt;"&amp;'Testi Menu'!$B$6&amp;"&lt;/span&gt;&lt;span class=""riga2""&gt;"&amp;'Testi Menu'!$B$7&amp;"&lt;/span&gt;&lt;span class=""anno""&gt;"&amp;'Testi Menu'!$B$8&amp;"&lt;/span&gt;&lt;/h1&gt;"</f>
         <v>    &lt;h1 class="titolo"&gt;&lt;span class="riga1"&gt;Festa di&lt;/span&gt;&lt;span class="riga2"&gt;Sant'Agostino&lt;/span&gt;&lt;span class="anno"&gt;2026&lt;/span&gt;&lt;/h1&gt;</v>
       </c>
     </row>
-    <row r="295" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A295" s="42" t="str">
+    <row r="318" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A318" s="42" t="str">
         <f aca="false">"    &lt;p class=""sottotitolo""&gt;"&amp;'Testi Menu'!$B$9&amp;IF('Testi Menu'!$B$10="","","&lt;br&gt;"&amp;'Testi Menu'!$B$10)&amp;IF('Testi Menu'!$B$11="","","&lt;br&gt;"&amp;'Testi Menu'!$B$11)&amp;"&lt;/p&gt;"</f>
         <v>    &lt;p class="sottotitolo"&gt;Due weekend di piadine e hamburger!!&lt;br&gt;Si ordina alla cassa e si ritirano le bevande.&lt;br&gt;Il cibo verrà servito al tavolo.&lt;/p&gt;</v>
       </c>
     </row>
-    <row r="296" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A296" s="41" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="297" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A297" s="41" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="298" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A298" s="41"/>
-    </row>
-    <row r="299" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A299" s="41" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="300" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A300" s="41" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="301" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A301" s="42" t="str">
+    <row r="319" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A319" s="41" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="320" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A320" s="41" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="321" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A321" s="41"/>
+    </row>
+    <row r="322" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A322" s="41" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="323" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A323" s="41" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="324" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A324" s="42" t="str">
         <f aca="false">"    &lt;li&gt;&lt;a href=""#cucina""&gt;"&amp;'Testi Menu'!$B$13&amp;"&lt;/a&gt;&lt;/li&gt;"</f>
         <v>    &lt;li&gt;&lt;a href="#cucina"&gt;Cucina&lt;/a&gt;&lt;/li&gt;</v>
       </c>
     </row>
-    <row r="302" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A302" s="42" t="str">
+    <row r="325" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A325" s="42" t="str">
         <f aca="false">"    &lt;li&gt;&lt;a href=""#fritti""&gt;"&amp;'Testi Menu'!$B$15&amp;"&lt;/a&gt;&lt;/li&gt;"</f>
         <v>    &lt;li&gt;&lt;a href="#fritti"&gt;Fritti&lt;/a&gt;&lt;/li&gt;</v>
       </c>
     </row>
-    <row r="303" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A303" s="42" t="str">
+    <row r="326" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A326" s="42" t="str">
         <f aca="false">"    &lt;li&gt;&lt;a href=""#bevande""&gt;"&amp;'Testi Menu'!$B$17&amp;"&lt;/a&gt;&lt;/li&gt;"</f>
         <v>    &lt;li&gt;&lt;a href="#bevande"&gt;Bevande&lt;/a&gt;&lt;/li&gt;</v>
       </c>
     </row>
-    <row r="304" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A304" s="41" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="305" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A305" s="41" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="306" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A306" s="41"/>
-    </row>
-    <row r="307" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A307" s="41" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="308" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A308" s="41"/>
-    </row>
-    <row r="309" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A309" s="41" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="310" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A310" s="41" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="311" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A311" s="42" t="str">
+    <row r="327" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A327" s="41" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="328" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A328" s="41" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="329" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A329" s="41"/>
+    </row>
+    <row r="330" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A330" s="41" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="331" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A331" s="41"/>
+    </row>
+    <row r="332" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A332" s="41" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="333" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A333" s="41" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="334" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A334" s="42" t="str">
         <f aca="false">"      &lt;h2&gt;"&amp;'Testi Menu'!$B$13&amp;"&lt;/h2&gt;"</f>
         <v>      &lt;h2&gt;Cucina&lt;/h2&gt;</v>
       </c>
     </row>
-    <row r="312" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A312" s="42" t="str">
+    <row r="335" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A335" s="42" t="str">
         <f aca="false">"      &lt;p&gt;"&amp;'Testi Menu'!$B$14&amp;"&lt;/p&gt;"</f>
         <v>      &lt;p&gt;Piadine e hamburger&lt;/p&gt;</v>
       </c>
     </row>
-    <row r="313" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A313" s="41" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="314" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A314" s="41" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="315" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A315" s="41" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="316" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A316" s="43" t="str">
+    <row r="336" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A336" s="41" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="337" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A337" s="41" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="338" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A338" s="41" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="339" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A339" s="43" t="str">
         <f aca="false">"        &lt;span class=""nome""&gt;"&amp;'Prodotti Finiti'!$V$2&amp;IF('Prodotti Finiti'!$W$2="","","&lt;em&gt;"&amp;'Prodotti Finiti'!$W$2&amp;"&lt;/em&gt;")&amp;"&lt;/span&gt;"</f>
         <v>        &lt;span class="nome"&gt;Piadina prosciutto crudo&lt;/span&gt;</v>
       </c>
     </row>
-    <row r="317" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A317" s="41" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="318" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A318" s="44" t="str">
+    <row r="340" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A340" s="41" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="341" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A341" s="44" t="str">
         <f aca="false">"        &lt;span class=""prezzo""&gt;"&amp;INT('Prodotti Finiti'!$B$2)&amp;","&amp;RIGHT("0"&amp;ROUND(MOD('Prodotti Finiti'!$B$2,1)*100,0),2)&amp;"&lt;/span&gt;"</f>
         <v>        &lt;span class="prezzo"&gt;5,50&lt;/span&gt;</v>
       </c>
     </row>
-    <row r="319" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A319" s="41" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="320" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A320" s="41" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="321" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A321" s="43" t="str">
+    <row r="342" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A342" s="41" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="343" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A343" s="41" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="344" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A344" s="43" t="str">
         <f aca="false">"        &lt;span class=""nome""&gt;"&amp;'Prodotti Finiti'!$V$3&amp;IF('Prodotti Finiti'!$W$3="","","&lt;em&gt;"&amp;'Prodotti Finiti'!$W$3&amp;"&lt;/em&gt;")&amp;"&lt;/span&gt;"</f>
         <v>        &lt;span class="nome"&gt;Piadina prosciutto crudo e formaggio&lt;/span&gt;</v>
       </c>
     </row>
-    <row r="322" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A322" s="41" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="323" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A323" s="44" t="str">
+    <row r="345" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A345" s="41" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="346" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A346" s="44" t="str">
         <f aca="false">"        &lt;span class=""prezzo""&gt;"&amp;INT('Prodotti Finiti'!$B$3)&amp;","&amp;RIGHT("0"&amp;ROUND(MOD('Prodotti Finiti'!$B$3,1)*100,0),2)&amp;"&lt;/span&gt;"</f>
         <v>        &lt;span class="prezzo"&gt;5,50&lt;/span&gt;</v>
       </c>
     </row>
-    <row r="324" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A324" s="41" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="325" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A325" s="41" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="326" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A326" s="43" t="str">
+    <row r="347" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A347" s="41" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="348" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A348" s="41" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="349" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A349" s="43" t="str">
         <f aca="false">"        &lt;span class=""nome""&gt;"&amp;'Prodotti Finiti'!$V$6&amp;IF('Prodotti Finiti'!$W$6="","","&lt;em&gt;"&amp;'Prodotti Finiti'!$W$6&amp;"&lt;/em&gt;")&amp;"&lt;/span&gt;"</f>
         <v>        &lt;span class="nome"&gt;Piadina salame ferrarese&lt;/span&gt;</v>
       </c>
     </row>
-    <row r="327" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A327" s="41" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="328" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A328" s="44" t="str">
+    <row r="350" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A350" s="41" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="351" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A351" s="44" t="str">
         <f aca="false">"        &lt;span class=""prezzo""&gt;"&amp;INT('Prodotti Finiti'!$B$6)&amp;","&amp;RIGHT("0"&amp;ROUND(MOD('Prodotti Finiti'!$B$6,1)*100,0),2)&amp;"&lt;/span&gt;"</f>
         <v>        &lt;span class="prezzo"&gt;5,50&lt;/span&gt;</v>
       </c>
     </row>
-    <row r="329" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A329" s="41" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="330" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A330" s="41" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="331" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A331" s="43" t="str">
+    <row r="352" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A352" s="41" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="353" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A353" s="41" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="354" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A354" s="43" t="str">
         <f aca="false">"        &lt;span class=""nome""&gt;"&amp;'Prodotti Finiti'!$V$7&amp;IF('Prodotti Finiti'!$W$7="","","&lt;em&gt;"&amp;'Prodotti Finiti'!$W$7&amp;"&lt;/em&gt;")&amp;"&lt;/span&gt;"</f>
         <v>        &lt;span class="nome"&gt;Piadina salame ferrarese e formaggio&lt;/span&gt;</v>
       </c>
     </row>
-    <row r="332" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A332" s="41" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="333" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A333" s="44" t="str">
+    <row r="355" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A355" s="41" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="356" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A356" s="44" t="str">
         <f aca="false">"        &lt;span class=""prezzo""&gt;"&amp;INT('Prodotti Finiti'!$B$7)&amp;","&amp;RIGHT("0"&amp;ROUND(MOD('Prodotti Finiti'!$B$7,1)*100,0),2)&amp;"&lt;/span&gt;"</f>
         <v>        &lt;span class="prezzo"&gt;5,50&lt;/span&gt;</v>
       </c>
     </row>
-    <row r="334" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A334" s="41" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="335" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A335" s="41" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="336" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A336" s="43" t="str">
+    <row r="357" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A357" s="41" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="358" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A358" s="41" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="359" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A359" s="43" t="str">
         <f aca="false">"        &lt;span class=""nome""&gt;"&amp;'Prodotti Finiti'!$V$4&amp;IF('Prodotti Finiti'!$W$4="","","&lt;em&gt;"&amp;'Prodotti Finiti'!$W$4&amp;"&lt;/em&gt;")&amp;"&lt;/span&gt;"</f>
         <v>        &lt;span class="nome"&gt;Piadina prosciutto cotto&lt;/span&gt;</v>
       </c>
     </row>
-    <row r="337" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A337" s="41" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="338" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A338" s="44" t="str">
+    <row r="360" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A360" s="41" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="361" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A361" s="44" t="str">
         <f aca="false">"        &lt;span class=""prezzo""&gt;"&amp;INT('Prodotti Finiti'!$B$4)&amp;","&amp;RIGHT("0"&amp;ROUND(MOD('Prodotti Finiti'!$B$4,1)*100,0),2)&amp;"&lt;/span&gt;"</f>
         <v>        &lt;span class="prezzo"&gt;5,00&lt;/span&gt;</v>
       </c>
     </row>
-    <row r="339" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A339" s="41" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="340" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A340" s="41" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="341" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A341" s="43" t="str">
+    <row r="362" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A362" s="41" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="363" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A363" s="41" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="364" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A364" s="43" t="str">
         <f aca="false">"        &lt;span class=""nome""&gt;"&amp;'Prodotti Finiti'!$V$5&amp;IF('Prodotti Finiti'!$W$5="","","&lt;em&gt;"&amp;'Prodotti Finiti'!$W$5&amp;"&lt;/em&gt;")&amp;"&lt;/span&gt;"</f>
         <v>        &lt;span class="nome"&gt;Piadina prosciutto cotto e formaggio&lt;/span&gt;</v>
       </c>
     </row>
-    <row r="342" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A342" s="41" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="343" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A343" s="44" t="str">
+    <row r="365" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A365" s="41" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="366" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A366" s="44" t="str">
         <f aca="false">"        &lt;span class=""prezzo""&gt;"&amp;INT('Prodotti Finiti'!$B$5)&amp;","&amp;RIGHT("0"&amp;ROUND(MOD('Prodotti Finiti'!$B$5,1)*100,0),2)&amp;"&lt;/span&gt;"</f>
         <v>        &lt;span class="prezzo"&gt;5,00&lt;/span&gt;</v>
       </c>
     </row>
-    <row r="344" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A344" s="41" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="345" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A345" s="41" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="346" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A346" s="43" t="str">
+    <row r="367" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A367" s="41" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="368" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A368" s="41" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="369" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A369" s="43" t="str">
         <f aca="false">"        &lt;span class=""nome""&gt;"&amp;'Prodotti Finiti'!$V$8&amp;IF('Prodotti Finiti'!$W$8="","","&lt;em&gt;"&amp;'Prodotti Finiti'!$W$8&amp;"&lt;/em&gt;")&amp;"&lt;/span&gt;"</f>
         <v>        &lt;span class="nome"&gt;Piadina solo formaggio&lt;/span&gt;</v>
       </c>
     </row>
-    <row r="347" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A347" s="41" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="348" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A348" s="44" t="str">
+    <row r="370" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A370" s="41" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="371" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A371" s="44" t="str">
         <f aca="false">"        &lt;span class=""prezzo""&gt;"&amp;INT('Prodotti Finiti'!$B$8)&amp;","&amp;RIGHT("0"&amp;ROUND(MOD('Prodotti Finiti'!$B$8,1)*100,0),2)&amp;"&lt;/span&gt;"</f>
         <v>        &lt;span class="prezzo"&gt;5,00&lt;/span&gt;</v>
       </c>
     </row>
-    <row r="349" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A349" s="41" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="350" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A350" s="41" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="351" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A351" s="43" t="str">
+    <row r="372" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A372" s="41" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="373" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A373" s="41" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="374" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A374" s="43" t="str">
         <f aca="false">"        &lt;span class=""nome""&gt;"&amp;'Prodotti Finiti'!$V$9&amp;IF('Prodotti Finiti'!$W$9="","","&lt;em&gt;"&amp;'Prodotti Finiti'!$W$9&amp;"&lt;/em&gt;")&amp;"&lt;/span&gt;"</f>
         <v>        &lt;span class="nome"&gt;Piatto hamburger&lt;em&gt;Carne del macellaio, pomodoro, insalata, maionese e ketchup, con patatine fritte&lt;/em&gt;&lt;/span&gt;</v>
       </c>
     </row>
-    <row r="352" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A352" s="41" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="353" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A353" s="44" t="str">
+    <row r="375" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A375" s="41" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="376" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A376" s="44" t="str">
         <f aca="false">"        &lt;span class=""prezzo""&gt;"&amp;INT('Prodotti Finiti'!$B$9)&amp;","&amp;RIGHT("0"&amp;ROUND(MOD('Prodotti Finiti'!$B$9,1)*100,0),2)&amp;"&lt;/span&gt;"</f>
         <v>        &lt;span class="prezzo"&gt;9,50&lt;/span&gt;</v>
       </c>
     </row>
-    <row r="354" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A354" s="41" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="355" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A355" s="41" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="356" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A356" s="41" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="357" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A357" s="41"/>
-    </row>
-    <row r="358" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A358" s="41" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="359" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A359" s="41" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="360" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A360" s="42" t="str">
+    <row r="377" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A377" s="41" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="378" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A378" s="41" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="379" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A379" s="41" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="380" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A380" s="41"/>
+    </row>
+    <row r="381" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A381" s="41" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="382" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A382" s="41" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="383" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A383" s="42" t="str">
         <f aca="false">"      &lt;h2&gt;"&amp;'Testi Menu'!$B$15&amp;"&lt;/h2&gt;"</f>
         <v>      &lt;h2&gt;Fritti&lt;/h2&gt;</v>
       </c>
     </row>
-    <row r="361" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A361" s="42" t="str">
+    <row r="384" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A384" s="42" t="str">
         <f aca="false">"      &lt;p&gt;"&amp;'Testi Menu'!$B$16&amp;"&lt;/p&gt;"</f>
         <v>      &lt;p&gt;Dalla friggitrice&lt;/p&gt;</v>
       </c>
     </row>
-    <row r="362" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A362" s="41" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="363" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A363" s="41" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="364" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A364" s="41" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="365" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A365" s="43" t="str">
+    <row r="385" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A385" s="41" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="386" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A386" s="41" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="387" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A387" s="41" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="388" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A388" s="43" t="str">
         <f aca="false">"        &lt;span class=""nome""&gt;"&amp;'Prodotti Finiti'!$V$10&amp;IF('Prodotti Finiti'!$W$10="","","&lt;em&gt;"&amp;'Prodotti Finiti'!$W$10&amp;"&lt;/em&gt;")&amp;"&lt;/span&gt;"</f>
         <v>        &lt;span class="nome"&gt;Patatine fritte&lt;em&gt;Con ketchup e maionese&lt;/em&gt;&lt;/span&gt;</v>
       </c>
     </row>
-    <row r="366" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A366" s="41" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="367" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A367" s="44" t="str">
+    <row r="389" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A389" s="41" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="390" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A390" s="44" t="str">
         <f aca="false">"        &lt;span class=""prezzo""&gt;"&amp;INT('Prodotti Finiti'!$B$10)&amp;","&amp;RIGHT("0"&amp;ROUND(MOD('Prodotti Finiti'!$B$10,1)*100,0),2)&amp;"&lt;/span&gt;"</f>
         <v>        &lt;span class="prezzo"&gt;3,00&lt;/span&gt;</v>
       </c>
     </row>
-    <row r="368" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A368" s="41" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="369" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A369" s="41" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="370" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A370" s="41" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="371" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A371" s="41"/>
-    </row>
-    <row r="372" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A372" s="41" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="373" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A373" s="41" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="374" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A374" s="42" t="str">
+    <row r="391" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A391" s="41" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="392" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A392" s="41" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="393" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A393" s="41" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="394" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A394" s="41"/>
+    </row>
+    <row r="395" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A395" s="41" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="396" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A396" s="41" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="397" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A397" s="42" t="str">
         <f aca="false">"      &lt;h2&gt;"&amp;'Testi Menu'!$B$17&amp;"&lt;/h2&gt;"</f>
         <v>      &lt;h2&gt;Bevande&lt;/h2&gt;</v>
       </c>
     </row>
-    <row r="375" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A375" s="42" t="str">
+    <row r="398" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A398" s="42" t="str">
         <f aca="false">"      &lt;p&gt;"&amp;'Testi Menu'!$B$18&amp;"&lt;/p&gt;"</f>
         <v>      &lt;p&gt;Spina e bottiglia&lt;/p&gt;</v>
       </c>
     </row>
-    <row r="376" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A376" s="41" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="377" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A377" s="41" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="378" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A378" s="41" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="379" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A379" s="43" t="str">
+    <row r="399" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A399" s="41" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="400" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A400" s="41" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="401" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A401" s="41" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="402" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A402" s="43" t="str">
         <f aca="false">"        &lt;span class=""nome""&gt;"&amp;'Prodotti Finiti'!$V$21&amp;IF('Prodotti Finiti'!$W$21="","","&lt;em&gt;"&amp;'Prodotti Finiti'!$W$21&amp;"&lt;/em&gt;")&amp;"&lt;/span&gt;"</f>
         <v>        &lt;span class="nome"&gt;Birra bionda&lt;em&gt;Alla spina&lt;/em&gt;&lt;/span&gt;</v>
       </c>
     </row>
-    <row r="380" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A380" s="41" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="381" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A381" s="41" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="382" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A382" s="44" t="str">
+    <row r="403" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A403" s="41" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="404" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A404" s="41" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="405" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A405" s="44" t="str">
         <f aca="false">"          &lt;span class=""formato""&gt;&lt;small&gt;0,2 L&lt;/small&gt;&lt;span class=""prezzo""&gt;"&amp;INT('Prodotti Finiti'!$B$21)&amp;","&amp;RIGHT("0"&amp;ROUND(MOD('Prodotti Finiti'!$B$21,1)*100,0),2)&amp;"&lt;/span&gt;&lt;/span&gt;"</f>
         <v>          &lt;span class="formato"&gt;&lt;small&gt;0,2 L&lt;/small&gt;&lt;span class="prezzo"&gt;2,50&lt;/span&gt;&lt;/span&gt;</v>
       </c>
     </row>
-    <row r="383" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A383" s="44" t="str">
+    <row r="406" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A406" s="44" t="str">
         <f aca="false">"          &lt;span class=""formato""&gt;&lt;small&gt;0,4 L&lt;/small&gt;&lt;span class=""prezzo""&gt;"&amp;INT('Prodotti Finiti'!$B$22)&amp;","&amp;RIGHT("0"&amp;ROUND(MOD('Prodotti Finiti'!$B$22,1)*100,0),2)&amp;"&lt;/span&gt;&lt;/span&gt;"</f>
         <v>          &lt;span class="formato"&gt;&lt;small&gt;0,4 L&lt;/small&gt;&lt;span class="prezzo"&gt;4,00&lt;/span&gt;&lt;/span&gt;</v>
       </c>
     </row>
-    <row r="384" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A384" s="41" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="385" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A385" s="41" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="386" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A386" s="41" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="387" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A387" s="43" t="str">
+    <row r="407" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A407" s="41" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="408" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A408" s="41" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="409" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A409" s="41" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="410" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A410" s="43" t="str">
         <f aca="false">"        &lt;span class=""nome""&gt;"&amp;'Prodotti Finiti'!$V$19&amp;IF('Prodotti Finiti'!$W$19="","","&lt;em&gt;"&amp;'Prodotti Finiti'!$W$19&amp;"&lt;/em&gt;")&amp;"&lt;/span&gt;"</f>
         <v>        &lt;span class="nome"&gt;Birra rossa&lt;em&gt;Alla spina&lt;/em&gt;&lt;/span&gt;</v>
       </c>
     </row>
-    <row r="388" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A388" s="41" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="389" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A389" s="41" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="390" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A390" s="44" t="str">
+    <row r="411" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A411" s="41" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="412" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A412" s="41" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="413" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A413" s="44" t="str">
         <f aca="false">"          &lt;span class=""formato""&gt;&lt;small&gt;0,2 L&lt;/small&gt;&lt;span class=""prezzo""&gt;"&amp;INT('Prodotti Finiti'!$B$19)&amp;","&amp;RIGHT("0"&amp;ROUND(MOD('Prodotti Finiti'!$B$19,1)*100,0),2)&amp;"&lt;/span&gt;&lt;/span&gt;"</f>
         <v>          &lt;span class="formato"&gt;&lt;small&gt;0,2 L&lt;/small&gt;&lt;span class="prezzo"&gt;3,00&lt;/span&gt;&lt;/span&gt;</v>
       </c>
     </row>
-    <row r="391" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A391" s="44" t="str">
+    <row r="414" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A414" s="44" t="str">
         <f aca="false">"          &lt;span class=""formato""&gt;&lt;small&gt;0,4 L&lt;/small&gt;&lt;span class=""prezzo""&gt;"&amp;INT('Prodotti Finiti'!$B$20)&amp;","&amp;RIGHT("0"&amp;ROUND(MOD('Prodotti Finiti'!$B$20,1)*100,0),2)&amp;"&lt;/span&gt;&lt;/span&gt;"</f>
         <v>          &lt;span class="formato"&gt;&lt;small&gt;0,4 L&lt;/small&gt;&lt;span class="prezzo"&gt;5,00&lt;/span&gt;&lt;/span&gt;</v>
       </c>
     </row>
-    <row r="392" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A392" s="41" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="393" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A393" s="41" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="394" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A394" s="41" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="395" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A395" s="43" t="str">
+    <row r="415" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A415" s="41" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="416" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A416" s="41" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="417" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A417" s="41" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="418" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A418" s="43" t="str">
         <f aca="false">"        &lt;span class=""nome""&gt;"&amp;'Prodotti Finiti'!$V$13&amp;IF('Prodotti Finiti'!$W$13="","","&lt;em&gt;"&amp;'Prodotti Finiti'!$W$13&amp;"&lt;/em&gt;")&amp;"&lt;/span&gt;"</f>
         <v>        &lt;span class="nome"&gt;Coca Cola&lt;em&gt;Alla spina&lt;/em&gt;&lt;/span&gt;</v>
       </c>
     </row>
-    <row r="396" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A396" s="41" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="397" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A397" s="41" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="398" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A398" s="44" t="str">
+    <row r="419" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A419" s="41" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="420" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A420" s="41" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="421" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A421" s="44" t="str">
         <f aca="false">"          &lt;span class=""formato""&gt;&lt;small&gt;0,2 L&lt;/small&gt;&lt;span class=""prezzo""&gt;"&amp;INT('Prodotti Finiti'!$B$13)&amp;","&amp;RIGHT("0"&amp;ROUND(MOD('Prodotti Finiti'!$B$13,1)*100,0),2)&amp;"&lt;/span&gt;&lt;/span&gt;"</f>
         <v>          &lt;span class="formato"&gt;&lt;small&gt;0,2 L&lt;/small&gt;&lt;span class="prezzo"&gt;2,50&lt;/span&gt;&lt;/span&gt;</v>
       </c>
     </row>
-    <row r="399" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A399" s="44" t="str">
+    <row r="422" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A422" s="44" t="str">
         <f aca="false">"          &lt;span class=""formato""&gt;&lt;small&gt;0,4 L&lt;/small&gt;&lt;span class=""prezzo""&gt;"&amp;INT('Prodotti Finiti'!$B$14)&amp;","&amp;RIGHT("0"&amp;ROUND(MOD('Prodotti Finiti'!$B$14,1)*100,0),2)&amp;"&lt;/span&gt;&lt;/span&gt;"</f>
         <v>          &lt;span class="formato"&gt;&lt;small&gt;0,4 L&lt;/small&gt;&lt;span class="prezzo"&gt;4,00&lt;/span&gt;&lt;/span&gt;</v>
       </c>
     </row>
-    <row r="400" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A400" s="41" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="401" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A401" s="41" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="402" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A402" s="41" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="403" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A403" s="43" t="str">
+    <row r="423" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A423" s="41" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="424" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A424" s="41" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="425" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A425" s="41" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="426" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A426" s="43" t="str">
         <f aca="false">"        &lt;span class=""nome""&gt;"&amp;'Prodotti Finiti'!$V$23&amp;IF('Prodotti Finiti'!$W$23="","","&lt;em&gt;"&amp;'Prodotti Finiti'!$W$23&amp;"&lt;/em&gt;")&amp;"&lt;/span&gt;"</f>
         <v>        &lt;span class="nome"&gt;Vino bianco frizzante&lt;em&gt;Alla spina&lt;/em&gt;&lt;/span&gt;</v>
       </c>
     </row>
-    <row r="404" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A404" s="41" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="405" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A405" s="41" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="406" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A406" s="44" t="str">
+    <row r="427" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A427" s="41" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="428" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A428" s="41" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="429" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A429" s="44" t="str">
         <f aca="false">"          &lt;span class=""formato""&gt;&lt;small&gt;0,2 L&lt;/small&gt;&lt;span class=""prezzo""&gt;"&amp;INT('Prodotti Finiti'!$B$23)&amp;","&amp;RIGHT("0"&amp;ROUND(MOD('Prodotti Finiti'!$B$23,1)*100,0),2)&amp;"&lt;/span&gt;&lt;/span&gt;"</f>
         <v>          &lt;span class="formato"&gt;&lt;small&gt;0,2 L&lt;/small&gt;&lt;span class="prezzo"&gt;2,50&lt;/span&gt;&lt;/span&gt;</v>
       </c>
     </row>
-    <row r="407" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A407" s="41" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="408" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A408" s="41" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="409" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A409" s="41" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="410" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A410" s="43" t="str">
+    <row r="430" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A430" s="41" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="431" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A431" s="41" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="432" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A432" s="41" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="433" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A433" s="43" t="str">
         <f aca="false">"        &lt;span class=""nome""&gt;"&amp;'Prodotti Finiti'!$V$24&amp;IF('Prodotti Finiti'!$W$24="","","&lt;em&gt;"&amp;'Prodotti Finiti'!$W$24&amp;"&lt;/em&gt;")&amp;"&lt;/span&gt;"</f>
         <v>        &lt;span class="nome"&gt;Spritz Aperol&lt;/span&gt;</v>
       </c>
     </row>
-    <row r="411" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A411" s="41" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="412" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A412" s="44" t="str">
+    <row r="434" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A434" s="41" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="435" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A435" s="44" t="str">
         <f aca="false">"        &lt;span class=""prezzo""&gt;"&amp;INT('Prodotti Finiti'!$B$24)&amp;","&amp;RIGHT("0"&amp;ROUND(MOD('Prodotti Finiti'!$B$24,1)*100,0),2)&amp;"&lt;/span&gt;"</f>
         <v>        &lt;span class="prezzo"&gt;3,50&lt;/span&gt;</v>
       </c>
     </row>
-    <row r="413" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A413" s="41" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="414" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A414" s="41" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="415" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A415" s="43" t="str">
+    <row r="436" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A436" s="41" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="437" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A437" s="41" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="438" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A438" s="43" t="str">
         <f aca="false">"        &lt;span class=""nome""&gt;"&amp;'Prodotti Finiti'!$V$25&amp;IF('Prodotti Finiti'!$W$25="","","&lt;em&gt;"&amp;'Prodotti Finiti'!$W$25&amp;"&lt;/em&gt;")&amp;"&lt;/span&gt;"</f>
         <v>        &lt;span class="nome"&gt;Spritz Campari&lt;/span&gt;</v>
       </c>
     </row>
-    <row r="416" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A416" s="41" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="417" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A417" s="44" t="str">
+    <row r="439" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A439" s="41" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="440" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A440" s="44" t="str">
         <f aca="false">"        &lt;span class=""prezzo""&gt;"&amp;INT('Prodotti Finiti'!$B$25)&amp;","&amp;RIGHT("0"&amp;ROUND(MOD('Prodotti Finiti'!$B$25,1)*100,0),2)&amp;"&lt;/span&gt;"</f>
         <v>        &lt;span class="prezzo"&gt;3,50&lt;/span&gt;</v>
       </c>
     </row>
-    <row r="418" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A418" s="41" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="419" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A419" s="41" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="420" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A420" s="43" t="str">
+    <row r="441" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A441" s="41" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="442" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A442" s="41" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="443" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A443" s="43" t="str">
         <f aca="false">"        &lt;span class=""nome""&gt;"&amp;'Prodotti Finiti'!$V$15&amp;IF('Prodotti Finiti'!$W$15="","","&lt;em&gt;"&amp;'Prodotti Finiti'!$W$15&amp;"&lt;/em&gt;")&amp;"&lt;/span&gt;"</f>
         <v>        &lt;span class="nome"&gt;Sprite&lt;em&gt;Lattina 0,33 L&lt;/em&gt;&lt;/span&gt;</v>
       </c>
     </row>
-    <row r="421" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A421" s="41" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="422" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A422" s="44" t="str">
+    <row r="444" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A444" s="41" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="445" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A445" s="44" t="str">
         <f aca="false">"        &lt;span class=""prezzo""&gt;"&amp;INT('Prodotti Finiti'!$B$15)&amp;","&amp;RIGHT("0"&amp;ROUND(MOD('Prodotti Finiti'!$B$15,1)*100,0),2)&amp;"&lt;/span&gt;"</f>
         <v>        &lt;span class="prezzo"&gt;2,00&lt;/span&gt;</v>
       </c>
     </row>
-    <row r="423" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A423" s="41" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="424" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A424" s="41" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="425" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A425" s="43" t="str">
+    <row r="446" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A446" s="41" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="447" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A447" s="41" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="448" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A448" s="43" t="str">
         <f aca="false">"        &lt;span class=""nome""&gt;"&amp;'Prodotti Finiti'!$V$16&amp;IF('Prodotti Finiti'!$W$16="","","&lt;em&gt;"&amp;'Prodotti Finiti'!$W$16&amp;"&lt;/em&gt;")&amp;"&lt;/span&gt;"</f>
         <v>        &lt;span class="nome"&gt;Coca Cola senza caffeina&lt;em&gt;Lattina 0,33 L&lt;/em&gt;&lt;/span&gt;</v>
       </c>
     </row>
-    <row r="426" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A426" s="41" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="427" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A427" s="44" t="str">
+    <row r="449" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A449" s="41" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="450" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A450" s="44" t="str">
         <f aca="false">"        &lt;span class=""prezzo""&gt;"&amp;INT('Prodotti Finiti'!$B$16)&amp;","&amp;RIGHT("0"&amp;ROUND(MOD('Prodotti Finiti'!$B$16,1)*100,0),2)&amp;"&lt;/span&gt;"</f>
         <v>        &lt;span class="prezzo"&gt;2,00&lt;/span&gt;</v>
       </c>
     </row>
-    <row r="428" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A428" s="41" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="429" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A429" s="41" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="430" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A430" s="43" t="str">
+    <row r="451" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A451" s="41" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="452" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A452" s="41" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="453" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A453" s="43" t="str">
         <f aca="false">"        &lt;span class=""nome""&gt;"&amp;'Prodotti Finiti'!$V$17&amp;IF('Prodotti Finiti'!$W$17="","","&lt;em&gt;"&amp;'Prodotti Finiti'!$W$17&amp;"&lt;/em&gt;")&amp;"&lt;/span&gt;"</f>
         <v>        &lt;span class="nome"&gt;Tè al limone&lt;em&gt;Lattina 0,33 L&lt;/em&gt;&lt;/span&gt;</v>
       </c>
     </row>
-    <row r="431" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A431" s="41" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="432" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A432" s="44" t="str">
+    <row r="454" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A454" s="41" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="455" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A455" s="44" t="str">
         <f aca="false">"        &lt;span class=""prezzo""&gt;"&amp;INT('Prodotti Finiti'!$B$17)&amp;","&amp;RIGHT("0"&amp;ROUND(MOD('Prodotti Finiti'!$B$17,1)*100,0),2)&amp;"&lt;/span&gt;"</f>
         <v>        &lt;span class="prezzo"&gt;2,00&lt;/span&gt;</v>
       </c>
     </row>
-    <row r="433" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A433" s="41" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="434" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A434" s="41" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="435" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A435" s="43" t="str">
+    <row r="456" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A456" s="41" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="457" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A457" s="41" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="458" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A458" s="43" t="str">
         <f aca="false">"        &lt;span class=""nome""&gt;"&amp;'Prodotti Finiti'!$V$18&amp;IF('Prodotti Finiti'!$W$18="","","&lt;em&gt;"&amp;'Prodotti Finiti'!$W$18&amp;"&lt;/em&gt;")&amp;"&lt;/span&gt;"</f>
         <v>        &lt;span class="nome"&gt;Tè alla pesca&lt;em&gt;Lattina 0,33 L&lt;/em&gt;&lt;/span&gt;</v>
       </c>
     </row>
-    <row r="436" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A436" s="41" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="437" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A437" s="44" t="str">
+    <row r="459" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A459" s="41" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="460" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A460" s="44" t="str">
         <f aca="false">"        &lt;span class=""prezzo""&gt;"&amp;INT('Prodotti Finiti'!$B$18)&amp;","&amp;RIGHT("0"&amp;ROUND(MOD('Prodotti Finiti'!$B$18,1)*100,0),2)&amp;"&lt;/span&gt;"</f>
         <v>        &lt;span class="prezzo"&gt;2,00&lt;/span&gt;</v>
       </c>
     </row>
-    <row r="438" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A438" s="41" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="439" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A439" s="41" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="440" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A440" s="43" t="str">
+    <row r="461" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A461" s="41" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="462" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A462" s="41" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="463" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A463" s="43" t="str">
         <f aca="false">"        &lt;span class=""nome""&gt;"&amp;'Prodotti Finiti'!$V$11&amp;IF('Prodotti Finiti'!$W$11="","","&lt;em&gt;"&amp;'Prodotti Finiti'!$W$11&amp;"&lt;/em&gt;")&amp;"&lt;/span&gt;"</f>
         <v>        &lt;span class="nome"&gt;Acqua naturale&lt;em&gt;Bottiglia 0,5 L&lt;/em&gt;&lt;/span&gt;</v>
       </c>
     </row>
-    <row r="441" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A441" s="41" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="442" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A442" s="44" t="str">
+    <row r="464" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A464" s="41" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="465" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A465" s="44" t="str">
         <f aca="false">"        &lt;span class=""prezzo""&gt;"&amp;INT('Prodotti Finiti'!$B$11)&amp;","&amp;RIGHT("0"&amp;ROUND(MOD('Prodotti Finiti'!$B$11,1)*100,0),2)&amp;"&lt;/span&gt;"</f>
         <v>        &lt;span class="prezzo"&gt;1,00&lt;/span&gt;</v>
       </c>
     </row>
-    <row r="443" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A443" s="41" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="444" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A444" s="41" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="445" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A445" s="43" t="str">
+    <row r="466" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A466" s="41" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="467" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A467" s="41" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="468" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A468" s="43" t="str">
         <f aca="false">"        &lt;span class=""nome""&gt;"&amp;'Prodotti Finiti'!$V$12&amp;IF('Prodotti Finiti'!$W$12="","","&lt;em&gt;"&amp;'Prodotti Finiti'!$W$12&amp;"&lt;/em&gt;")&amp;"&lt;/span&gt;"</f>
         <v>        &lt;span class="nome"&gt;Acqua frizzante&lt;em&gt;Bottiglia 0,5 L&lt;/em&gt;&lt;/span&gt;</v>
       </c>
     </row>
-    <row r="446" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A446" s="41" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="447" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A447" s="44" t="str">
+    <row r="469" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A469" s="41" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="470" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A470" s="44" t="str">
         <f aca="false">"        &lt;span class=""prezzo""&gt;"&amp;INT('Prodotti Finiti'!$B$12)&amp;","&amp;RIGHT("0"&amp;ROUND(MOD('Prodotti Finiti'!$B$12,1)*100,0),2)&amp;"&lt;/span&gt;"</f>
         <v>        &lt;span class="prezzo"&gt;1,00&lt;/span&gt;</v>
       </c>
     </row>
-    <row r="448" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A448" s="41" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="449" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A449" s="41" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="450" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A450" s="41" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="451" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A451" s="41"/>
-    </row>
-    <row r="452" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A452" s="41" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="453" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A453" s="41"/>
-    </row>
-    <row r="454" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A454" s="41" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="455" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A455" s="41" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="456" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A456" s="41" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="457" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A457" s="41" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="458" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A458" s="41"/>
-    </row>
-    <row r="459" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A459" s="41" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="460" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A460" s="41" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="461" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A461" s="41" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="462" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A462" s="41" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="463" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A463" s="41" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="464" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A464" s="41" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="465" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A465" s="41" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="466" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A466" s="41" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="467" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A467" s="41" t="s">
+    <row r="471" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A471" s="41" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="468" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A468" s="41"/>
-    </row>
-    <row r="469" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A469" s="41"/>
-    </row>
-    <row r="470" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A470" s="41" t="s">
+    <row r="472" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A472" s="41" t="s">
         <v>405</v>
-      </c>
-    </row>
-    <row r="471" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A471" s="42" t="str">
-        <f aca="false">"  &lt;p&gt;"&amp;LEFT('Testi Menu'!$B$20,FIND(".",'Testi Menu'!$B$20))&amp;" &lt;strong&gt;"&amp;TRIM(MID('Testi Menu'!$B$20,FIND(".",'Testi Menu'!$B$20)+1,999))&amp;"&lt;/strong&gt;&lt;/p&gt;"</f>
-        <v>  &lt;p&gt;Prezzi in euro. &lt;strong&gt;Bicchieri e stoviglie compostabili.&lt;/strong&gt;&lt;/p&gt;</v>
-      </c>
-    </row>
-    <row r="472" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A472" s="42" t="str">
-        <f aca="false">"  &lt;p&gt;"&amp;'Testi Menu'!$B$21&amp;"&lt;/p&gt;"</f>
-        <v>  &lt;p&gt;Grazie per fare la differenziata negli appositi contenitori.&lt;/p&gt;</v>
       </c>
     </row>
     <row r="473" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11977,16 +12054,169 @@
     </row>
     <row r="475" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A475" s="41" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
     </row>
     <row r="476" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A476" s="41" t="s">
-        <v>408</v>
-      </c>
+      <c r="A476" s="41"/>
     </row>
     <row r="477" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A477" s="41"/>
+      <c r="A477" s="41" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="478" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A478" s="41" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="479" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A479" s="41" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="480" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A480" s="41" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="481" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A481" s="41"/>
+    </row>
+    <row r="482" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A482" s="41" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="483" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A483" s="41" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="484" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A484" s="41" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="485" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A485" s="41" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="486" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A486" s="41" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="487" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A487" s="41" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="488" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A488" s="41" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="489" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A489" s="41" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="490" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A490" s="41" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="491" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A491" s="41" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="492" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A492" s="41" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="493" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A493" s="41" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="494" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A494" s="41"/>
+    </row>
+    <row r="495" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A495" s="41"/>
+    </row>
+    <row r="496" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A496" s="41"/>
+    </row>
+    <row r="497" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A497" s="41" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="498" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A498" s="41" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="499" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A499" s="41" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="500" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A500" s="41" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="501" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A501" s="41" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="502" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A502" s="41"/>
+    </row>
+    <row r="503" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A503" s="41" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="504" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A504" s="42" t="str">
+        <f aca="false">"  &lt;p&gt;"&amp;LEFT('Testi Menu'!$B$20,FIND(".",'Testi Menu'!$B$20))&amp;" &lt;strong&gt;"&amp;TRIM(MID('Testi Menu'!$B$20,FIND(".",'Testi Menu'!$B$20)+1,999))&amp;"&lt;/strong&gt;&lt;/p&gt;"</f>
+        <v>  &lt;p&gt;Prezzi in euro. &lt;strong&gt;Bicchieri e stoviglie compostabili.&lt;/strong&gt;&lt;/p&gt;</v>
+      </c>
+    </row>
+    <row r="505" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A505" s="42" t="str">
+        <f aca="false">"  &lt;p&gt;"&amp;'Testi Menu'!$B$21&amp;"&lt;/p&gt;"</f>
+        <v>  &lt;p&gt;Grazie per fare la differenziata negli appositi contenitori.&lt;/p&gt;</v>
+      </c>
+    </row>
+    <row r="506" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A506" s="41" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="507" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A507" s="41"/>
+    </row>
+    <row r="508" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A508" s="41" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="509" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A509" s="41" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="510" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A510" s="41"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -12014,204 +12244,204 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="45" t="s">
-        <v>409</v>
+        <v>434</v>
       </c>
       <c r="B1" s="27"/>
       <c r="C1" s="27"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="30" t="s">
-        <v>410</v>
+        <v>435</v>
       </c>
       <c r="B2" s="30" t="s">
-        <v>411</v>
+        <v>436</v>
       </c>
       <c r="C2" s="30" t="s">
-        <v>412</v>
+        <v>437</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="46" t="s">
-        <v>413</v>
+        <v>438</v>
       </c>
       <c r="B3" s="47"/>
       <c r="C3" s="47"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>414</v>
+        <v>439</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>415</v>
+        <v>440</v>
       </c>
       <c r="C4" s="48" t="s">
-        <v>416</v>
+        <v>441</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>417</v>
+        <v>442</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>418</v>
+        <v>443</v>
       </c>
       <c r="C5" s="48"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>419</v>
+        <v>444</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>420</v>
+        <v>445</v>
       </c>
       <c r="C6" s="48"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>421</v>
+        <v>446</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>422</v>
+        <v>447</v>
       </c>
       <c r="C7" s="48" t="s">
-        <v>423</v>
+        <v>448</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>424</v>
+        <v>449</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>425</v>
+        <v>450</v>
       </c>
       <c r="C8" s="48" t="s">
-        <v>426</v>
+        <v>451</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>427</v>
+        <v>452</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>428</v>
+        <v>453</v>
       </c>
       <c r="C9" s="48"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>429</v>
+        <v>454</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>430</v>
+        <v>455</v>
       </c>
       <c r="C10" s="48" t="s">
-        <v>431</v>
+        <v>456</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>432</v>
+        <v>457</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>433</v>
+        <v>458</v>
       </c>
       <c r="C11" s="48" t="s">
-        <v>431</v>
+        <v>456</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="46" t="s">
-        <v>434</v>
+        <v>459</v>
       </c>
       <c r="B12" s="47"/>
       <c r="C12" s="47"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>435</v>
+        <v>460</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>436</v>
+        <v>461</v>
       </c>
       <c r="C13" s="48" t="s">
-        <v>437</v>
+        <v>462</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>438</v>
+        <v>463</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>439</v>
+        <v>464</v>
       </c>
       <c r="C14" s="48"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>440</v>
+        <v>465</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>441</v>
+        <v>466</v>
       </c>
       <c r="C15" s="48"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>442</v>
+        <v>467</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>443</v>
+        <v>468</v>
       </c>
       <c r="C16" s="48"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>444</v>
+        <v>469</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>445</v>
+        <v>470</v>
       </c>
       <c r="C17" s="48"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>446</v>
+        <v>471</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>447</v>
+        <v>472</v>
       </c>
       <c r="C18" s="48"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="46" t="s">
-        <v>448</v>
+        <v>473</v>
       </c>
       <c r="B19" s="47"/>
       <c r="C19" s="47"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>449</v>
+        <v>474</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>450</v>
+        <v>475</v>
       </c>
       <c r="C20" s="48" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
-        <v>452</v>
+        <v>477</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>453</v>
+        <v>478</v>
       </c>
       <c r="C21" s="48"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="17" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
     </row>
   </sheetData>
@@ -12238,7 +12468,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="49" t="s">
-        <v>455</v>
+        <v>480</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12246,17 +12476,17 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="50" t="s">
-        <v>456</v>
+        <v>481</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="50" t="s">
-        <v>457</v>
+        <v>482</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="50" t="s">
-        <v>458</v>
+        <v>483</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12264,17 +12494,17 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="50" t="s">
-        <v>459</v>
+        <v>484</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="50" t="s">
-        <v>460</v>
+        <v>485</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="50" t="s">
-        <v>461</v>
+        <v>486</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12282,7 +12512,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="50" t="s">
-        <v>462</v>
+        <v>487</v>
       </c>
     </row>
   </sheetData>
@@ -12320,57 +12550,57 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>463</v>
+        <v>488</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>464</v>
+        <v>489</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>465</v>
+        <v>490</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>466</v>
+        <v>491</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>467</v>
+        <v>492</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>468</v>
+        <v>493</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>469</v>
+        <v>494</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>470</v>
+        <v>495</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>471</v>
+        <v>496</v>
       </c>
       <c r="J1" s="51" t="s">
-        <v>472</v>
+        <v>497</v>
       </c>
       <c r="K1" s="52" t="s">
-        <v>473</v>
+        <v>498</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>474</v>
+        <v>499</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>475</v>
+        <v>500</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>476</v>
+        <v>501</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>477</v>
+        <v>502</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>478</v>
+        <v>503</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>479</v>
+        <v>504</v>
       </c>
       <c r="D2" s="18" t="n">
         <v>48</v>
@@ -12390,13 +12620,13 @@
         <v>1.1834</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>480</v>
+        <v>505</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>481</v>
+        <v>506</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>482</v>
+        <v>507</v>
       </c>
       <c r="M2" s="54" t="n">
         <f aca="false">IF(L2="Pane/Piadina",0.04,IF(OR(L2="Salumi",L2="Formaggio"),0.1,0.22))</f>
@@ -12409,13 +12639,13 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>483</v>
+        <v>508</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>484</v>
+        <v>509</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>479</v>
+        <v>504</v>
       </c>
       <c r="D3" s="18" t="n">
         <v>2</v>
@@ -12435,13 +12665,13 @@
         <v>28.731</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>480</v>
+        <v>505</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>481</v>
+        <v>506</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>482</v>
+        <v>507</v>
       </c>
       <c r="M3" s="54" t="n">
         <f aca="false">IF(L3="Pane/Piadina",0.04,IF(OR(L3="Salumi",L3="Formaggio"),0.1,0.22))</f>
@@ -12454,13 +12684,13 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>485</v>
+        <v>510</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>486</v>
+        <v>511</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>487</v>
+        <v>512</v>
       </c>
       <c r="D4" s="18" t="n">
         <v>12</v>
@@ -12480,13 +12710,13 @@
         <v>1.0004</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>480</v>
+        <v>505</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>481</v>
+        <v>506</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>482</v>
+        <v>507</v>
       </c>
       <c r="M4" s="54" t="n">
         <f aca="false">IF(L4="Pane/Piadina",0.04,IF(OR(L4="Salumi",L4="Formaggio"),0.1,0.22))</f>
@@ -12499,13 +12729,13 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>488</v>
+        <v>513</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>489</v>
+        <v>514</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>479</v>
+        <v>504</v>
       </c>
       <c r="D5" s="18" t="n">
         <v>20</v>
@@ -12525,13 +12755,13 @@
         <v>2.9402</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>480</v>
+        <v>505</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>481</v>
+        <v>506</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>482</v>
+        <v>507</v>
       </c>
       <c r="M5" s="54" t="n">
         <f aca="false">IF(L5="Pane/Piadina",0.04,IF(OR(L5="Salumi",L5="Formaggio"),0.1,0.22))</f>
@@ -12544,13 +12774,13 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>490</v>
+        <v>515</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>491</v>
+        <v>516</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>492</v>
+        <v>517</v>
       </c>
       <c r="D6" s="18" t="n">
         <v>1</v>
@@ -12570,13 +12800,13 @@
         <v>3.965</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>480</v>
+        <v>505</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>481</v>
+        <v>506</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>482</v>
+        <v>507</v>
       </c>
       <c r="M6" s="54" t="n">
         <f aca="false">IF(L6="Pane/Piadina",0.04,IF(OR(L6="Salumi",L6="Formaggio"),0.1,0.22))</f>
@@ -12589,13 +12819,13 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>493</v>
+        <v>518</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>494</v>
+        <v>519</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>492</v>
+        <v>517</v>
       </c>
       <c r="D7" s="18" t="n">
         <v>1</v>
@@ -12615,13 +12845,13 @@
         <v>12.261</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>480</v>
+        <v>505</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>481</v>
+        <v>506</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>482</v>
+        <v>507</v>
       </c>
       <c r="M7" s="54" t="n">
         <f aca="false">IF(L7="Pane/Piadina",0.04,IF(OR(L7="Salumi",L7="Formaggio"),0.1,0.22))</f>
@@ -12634,13 +12864,13 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>495</v>
+        <v>520</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>496</v>
+        <v>521</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>492</v>
+        <v>517</v>
       </c>
       <c r="D8" s="18" t="n">
         <v>1</v>
@@ -12660,13 +12890,13 @@
         <v>12.383</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>480</v>
+        <v>505</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>481</v>
+        <v>506</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>482</v>
+        <v>507</v>
       </c>
       <c r="M8" s="54" t="n">
         <f aca="false">IF(L8="Pane/Piadina",0.04,IF(OR(L8="Salumi",L8="Formaggio"),0.1,0.22))</f>
@@ -12679,13 +12909,13 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>497</v>
+        <v>522</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>498</v>
+        <v>523</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>492</v>
+        <v>517</v>
       </c>
       <c r="D9" s="18" t="n">
         <v>1</v>
@@ -12705,13 +12935,13 @@
         <v>11.44</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>480</v>
+        <v>505</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>481</v>
+        <v>506</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>499</v>
+        <v>524</v>
       </c>
       <c r="M9" s="54" t="n">
         <f aca="false">IF(L9="Pane/Piadina",0.04,IF(OR(L9="Salumi",L9="Formaggio"),0.1,0.22))</f>
@@ -12724,13 +12954,13 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>500</v>
+        <v>525</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>501</v>
+        <v>526</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>479</v>
+        <v>504</v>
       </c>
       <c r="D10" s="18" t="n">
         <v>8</v>
@@ -12750,13 +12980,13 @@
         <v>1.9656</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>480</v>
+        <v>505</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>481</v>
+        <v>506</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>502</v>
+        <v>527</v>
       </c>
       <c r="M10" s="54" t="n">
         <f aca="false">IF(L10="Pane/Piadina",0.04,IF(OR(L10="Salumi",L10="Formaggio"),0.1,0.22))</f>
@@ -12769,13 +12999,13 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>503</v>
+        <v>528</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>504</v>
+        <v>529</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>492</v>
+        <v>517</v>
       </c>
       <c r="D11" s="18" t="n">
         <v>1</v>
@@ -12795,13 +13025,13 @@
         <v>7.238</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>480</v>
+        <v>505</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>481</v>
+        <v>506</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>505</v>
+        <v>530</v>
       </c>
       <c r="M11" s="54" t="n">
         <f aca="false">IF(L11="Pane/Piadina",0.04,IF(OR(L11="Salumi",L11="Formaggio"),0.1,0.22))</f>
@@ -12814,13 +13044,13 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>506</v>
+        <v>531</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>507</v>
+        <v>532</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>479</v>
+        <v>504</v>
       </c>
       <c r="D12" s="18" t="n">
         <v>1</v>
@@ -12840,13 +13070,13 @@
         <v>14.19</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>480</v>
+        <v>505</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>481</v>
+        <v>506</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>499</v>
+        <v>524</v>
       </c>
       <c r="M12" s="54" t="n">
         <f aca="false">IF(L12="Pane/Piadina",0.04,IF(OR(L12="Salumi",L12="Formaggio"),0.1,0.22))</f>
@@ -12859,13 +13089,13 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>508</v>
+        <v>533</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>509</v>
+        <v>534</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>479</v>
+        <v>504</v>
       </c>
       <c r="D13" s="18" t="n">
         <v>1</v>
@@ -12885,13 +13115,13 @@
         <v>14.135</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>480</v>
+        <v>505</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>481</v>
+        <v>506</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>499</v>
+        <v>524</v>
       </c>
       <c r="M13" s="54" t="n">
         <f aca="false">IF(L13="Pane/Piadina",0.04,IF(OR(L13="Salumi",L13="Formaggio"),0.1,0.22))</f>
@@ -12904,13 +13134,13 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>510</v>
+        <v>535</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>511</v>
+        <v>536</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>479</v>
+        <v>504</v>
       </c>
       <c r="D14" s="18" t="n">
         <v>7</v>
@@ -12930,13 +13160,13 @@
         <v>1.2584</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>512</v>
+        <v>537</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>481</v>
+        <v>506</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>502</v>
+        <v>527</v>
       </c>
       <c r="M14" s="54" t="n">
         <f aca="false">IF(L14="Pane/Piadina",0.04,IF(OR(L14="Salumi",L14="Formaggio"),0.1,0.22))</f>
@@ -12949,7 +13179,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E16" s="55" t="s">
-        <v>513</v>
+        <v>538</v>
       </c>
       <c r="F16" s="5" t="n">
         <f aca="false">SUM(F2:F14)</f>
@@ -12999,42 +13229,42 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>514</v>
+        <v>539</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>515</v>
+        <v>540</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>516</v>
+        <v>541</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>517</v>
+        <v>542</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>518</v>
+        <v>543</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>475</v>
+        <v>500</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>519</v>
+        <v>544</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>520</v>
+        <v>545</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>521</v>
+        <v>546</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>522</v>
+        <v>547</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>523</v>
+        <v>548</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>524</v>
+        <v>549</v>
       </c>
       <c r="E2" s="18" t="n">
         <v>20</v>
@@ -13056,16 +13286,16 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>525</v>
+        <v>550</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>522</v>
+        <v>547</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>526</v>
+        <v>551</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>524</v>
+        <v>549</v>
       </c>
       <c r="E3" s="18" t="n">
         <v>15.3</v>
@@ -13087,16 +13317,16 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>527</v>
+        <v>552</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>522</v>
+        <v>547</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>528</v>
+        <v>553</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>524</v>
+        <v>549</v>
       </c>
       <c r="E4" s="18" t="n">
         <v>25</v>
@@ -13118,16 +13348,16 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>529</v>
+        <v>554</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>522</v>
+        <v>547</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>530</v>
+        <v>555</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>524</v>
+        <v>549</v>
       </c>
       <c r="E5" s="18" t="n">
         <v>18</v>
@@ -13149,16 +13379,16 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>531</v>
+        <v>556</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>522</v>
+        <v>547</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>532</v>
+        <v>557</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>533</v>
+        <v>558</v>
       </c>
       <c r="E6" s="18" t="n">
         <v>50</v>
@@ -13180,16 +13410,16 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>534</v>
+        <v>559</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>522</v>
+        <v>547</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>532</v>
+        <v>557</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>533</v>
+        <v>558</v>
       </c>
       <c r="E7" s="18" t="n">
         <v>50</v>
@@ -13211,16 +13441,16 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>535</v>
+        <v>560</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>522</v>
+        <v>547</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>536</v>
+        <v>561</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>537</v>
+        <v>562</v>
       </c>
       <c r="E8" s="18" t="n">
         <v>24</v>
@@ -13242,16 +13472,16 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>538</v>
+        <v>563</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>522</v>
+        <v>547</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>536</v>
+        <v>561</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>537</v>
+        <v>562</v>
       </c>
       <c r="E9" s="18" t="n">
         <v>24</v>
@@ -13273,16 +13503,16 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>539</v>
+        <v>564</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>522</v>
+        <v>547</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>532</v>
+        <v>557</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>533</v>
+        <v>558</v>
       </c>
       <c r="E10" s="18" t="n">
         <v>50</v>
@@ -13304,16 +13534,16 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>540</v>
+        <v>565</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>522</v>
+        <v>547</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>541</v>
+        <v>566</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>524</v>
+        <v>549</v>
       </c>
       <c r="E11" s="18" t="n">
         <v>1</v>
@@ -13335,16 +13565,16 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>542</v>
+        <v>567</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>522</v>
+        <v>547</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>541</v>
+        <v>566</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>524</v>
+        <v>549</v>
       </c>
       <c r="E12" s="18" t="n">
         <v>1</v>
@@ -13366,16 +13596,16 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>543</v>
+        <v>568</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>522</v>
+        <v>547</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>536</v>
+        <v>561</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>537</v>
+        <v>562</v>
       </c>
       <c r="E13" s="18" t="n">
         <v>24</v>
@@ -13397,16 +13627,16 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>544</v>
+        <v>569</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>522</v>
+        <v>547</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>536</v>
+        <v>561</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>537</v>
+        <v>562</v>
       </c>
       <c r="E14" s="18" t="n">
         <v>24</v>
@@ -13458,42 +13688,42 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>571</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="H1" s="2" t="s">
         <v>545</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>546</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>516</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>547</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>548</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>549</v>
+        <v>574</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>550</v>
+        <v>575</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>551</v>
+        <v>576</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>552</v>
+        <v>577</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>553</v>
+        <v>578</v>
       </c>
       <c r="F2" s="18" t="n">
         <v>12</v>
@@ -13508,19 +13738,19 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>554</v>
+        <v>579</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>550</v>
+        <v>575</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>555</v>
+        <v>580</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>552</v>
+        <v>577</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>553</v>
+        <v>578</v>
       </c>
       <c r="F3" s="18" t="n">
         <v>12</v>
@@ -13535,19 +13765,19 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>556</v>
+        <v>581</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>557</v>
+        <v>582</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>558</v>
+        <v>583</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>559</v>
+        <v>584</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>560</v>
+        <v>585</v>
       </c>
       <c r="F4" s="18" t="n">
         <v>2.5</v>
@@ -13562,19 +13792,19 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>561</v>
+        <v>586</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>562</v>
+        <v>587</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>563</v>
+        <v>588</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>564</v>
+        <v>589</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>560</v>
+        <v>585</v>
       </c>
       <c r="F5" s="18" t="n">
         <v>2</v>
@@ -13589,19 +13819,19 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>565</v>
+        <v>590</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>566</v>
+        <v>591</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>567</v>
+        <v>592</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>568</v>
+        <v>593</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>560</v>
+        <v>585</v>
       </c>
       <c r="F6" s="18" t="n">
         <v>0.4</v>
@@ -13616,19 +13846,19 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>569</v>
+        <v>594</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>570</v>
+        <v>595</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>571</v>
+        <v>596</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>572</v>
+        <v>597</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>560</v>
+        <v>585</v>
       </c>
       <c r="F7" s="18" t="n">
         <v>0.5</v>
